--- a/AAII_Financials/Quarterly/TILE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TILE_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
   <si>
     <t>TILE</t>
   </si>
@@ -656,406 +656,419 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45200</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45109</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45018</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44927</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44836</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44745</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44654</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44563</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44472</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44381</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44290</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44199</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44108</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44017</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43926</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43828</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43737</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43464</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43282</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43191</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43009</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42918</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42827</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42736</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>325100</v>
+      </c>
+      <c r="E8" s="3">
         <v>311000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>329600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>295800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>335600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>327800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>346600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>288000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>339600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>312700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>294800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>253300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>276900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>278600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>259500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>288200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>339500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>348400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>357500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>297700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>337100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>318300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>283600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>240600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>266200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>257400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>251700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>221100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>239500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>248300</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>202000</v>
+      </c>
+      <c r="E9" s="3">
         <v>200700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>217800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>199900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>230100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>219000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>229900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>181200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>218300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>206400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>185800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>157200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>180100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>176500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>162200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>173900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>196300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>212600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>216800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>181200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>215400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>218400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>174500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>147000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>164400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>158900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>153800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>133300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>149500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>155400</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>123100</v>
+      </c>
+      <c r="E10" s="3">
         <v>110300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>111800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>95900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>105500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>108800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>116700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>106800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>121300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>106300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>109000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>96100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>96800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>102100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>97300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>114300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>143200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>135800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>140700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>116500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>121700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>99900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>109100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>93600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>101800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>98500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>97900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>87800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>90000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>92900</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1088,8 +1101,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1180,8 +1194,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1272,8 +1289,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1281,65 +1301,65 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>-2600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>36600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-1500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>120100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>12300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>700</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>20500</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
@@ -1356,16 +1376,19 @@
         <v>0</v>
       </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>7300</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>19800</v>
       </c>
-      <c r="AF14" s="3" t="s">
+      <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1456,8 +1479,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1487,192 +1513,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>290000</v>
+      </c>
+      <c r="E17" s="3">
         <v>280000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>300700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>286300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>350100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>299700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>312100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>260600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>305700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>287900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>265600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>236400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>256000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>262800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>242100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>381700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>311500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>304700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>314600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>281300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>333200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>302500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>249900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>217600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>235300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>226100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>218200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>205300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>233100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>222600</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E18" s="3">
         <v>31000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>28900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>9500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-14500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>28100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>34500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>27400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>33900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>24800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>29200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>16900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>20900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>15800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>17400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-93500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>28000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>43700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>42900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>16400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>15800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>33700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>23000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>31000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>31300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>33500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>15800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>6400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>25700</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1705,468 +1738,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-6700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-200</v>
       </c>
       <c r="K20" s="3">
         <v>-200</v>
       </c>
       <c r="L20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M20" s="3">
         <v>-900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1500</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-1100</v>
       </c>
       <c r="T20" s="3">
         <v>-1100</v>
       </c>
       <c r="U20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="V20" s="3">
         <v>-300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>45200</v>
+      </c>
+      <c r="E21" s="3">
         <v>36000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>40900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>19300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-5600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>38900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>44600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>39300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>46300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>36700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>41800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>29500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>33500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>26100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>24400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-82700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>39500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>54900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>55300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>28600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>18300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>26500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>38900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>31200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>38300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>38000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>40300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>21400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>15900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>32500</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E22" s="3">
         <v>8200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>8300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>8500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>8100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>7700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>6900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7700</v>
-      </c>
-      <c r="M22" s="3">
-        <v>7300</v>
       </c>
       <c r="N22" s="3">
         <v>7300</v>
       </c>
       <c r="O22" s="3">
+        <v>7300</v>
+      </c>
+      <c r="P22" s="3">
         <v>13200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>5400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>5000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>5600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>5500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>6600</v>
-      </c>
-      <c r="U22" s="3">
-        <v>6800</v>
       </c>
       <c r="V22" s="3">
         <v>6800</v>
       </c>
       <c r="W22" s="3">
+        <v>6800</v>
+      </c>
+      <c r="X22" s="3">
         <v>6200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>4900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E23" s="3">
         <v>16100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>21100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-24600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>20200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>25900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>20400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>26300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>16200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>21300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-100600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>21400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>36100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>35800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>8600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>9400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>28200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>20400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>28200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>28400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>31100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>12800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>6400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E24" s="3">
         <v>6200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>6100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>9100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-13200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>9900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>6300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-2600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>7600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>8700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>9000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>10200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>4200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>7400</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2257,192 +2306,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E26" s="3">
         <v>9900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>15800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-24600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>14100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>16800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>13300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>21800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>11000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>15500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>19600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-102200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>16400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>26200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>29500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>7100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>8200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>20600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>15100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>19500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>19400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>20900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>8500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>4700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E27" s="3">
         <v>9800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>15600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-24200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>13800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>16500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>13100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>21800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>11000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>15500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>19600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-102200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>16400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>26200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>29500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>7100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>8200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>20600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>15100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>19500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>19400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>20900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>8500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>4700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2533,8 +2591,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2574,8 +2635,8 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
+      <c r="P29" s="3">
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>8</v>
@@ -2595,11 +2656,11 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
         <v>6700</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2607,11 +2668,11 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-15200</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2625,8 +2686,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2717,8 +2781,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2809,192 +2876,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E32" s="3">
         <v>6700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1400</v>
-      </c>
-      <c r="J32" s="3">
-        <v>200</v>
       </c>
       <c r="K32" s="3">
         <v>200</v>
       </c>
       <c r="L32" s="3">
+        <v>200</v>
+      </c>
+      <c r="M32" s="3">
         <v>900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1500</v>
-      </c>
-      <c r="S32" s="3">
-        <v>1100</v>
       </c>
       <c r="T32" s="3">
         <v>1100</v>
       </c>
       <c r="U32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V32" s="3">
         <v>300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E33" s="3">
         <v>9800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>15600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-24200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>13800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>16500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>13100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>21800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>11000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>15500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>19600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-102200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>16400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>26200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>29500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>7100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>6400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>8200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>20600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>15100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>4300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>19400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>20900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>8500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>4700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3085,197 +3161,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E35" s="3">
         <v>9800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>15600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-24200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>13800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>16500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>13100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>21800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>11000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>15500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>19600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-102200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>16400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>26200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>29500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>7100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>6400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>8200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>20600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>15100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>4300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>19400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>20900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>8500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>4700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45200</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45109</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45018</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44927</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44836</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44745</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44654</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44563</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44472</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44381</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44290</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44199</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44108</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44017</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43926</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43828</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43737</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43464</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43282</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43191</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43009</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42918</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42827</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42736</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3308,8 +3393,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3342,100 +3428,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>110500</v>
+      </c>
+      <c r="E41" s="3">
         <v>119600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>92900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>101300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>97600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>79400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>91700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>76100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>97300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>92800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>102400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>106900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>103100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>103700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>91800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>72700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>81300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>85200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>84300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>67000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>81000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>107300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>67000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>67900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>87000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>78100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>66800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>80000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>165700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>113700</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3526,376 +3616,391 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>163400</v>
+      </c>
+      <c r="E43" s="3">
         <v>143900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>166300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>147800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>182800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>170400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>174000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>145000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>171700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>153200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>146900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>128600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>139900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>132600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>139400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>145300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>177500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>176700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>183900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>165000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>179000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>177800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>156600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>137900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>142800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>133900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>136600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>116700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>126000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>128700</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>279100</v>
+      </c>
+      <c r="E44" s="3">
         <v>289300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>288200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>312700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>306300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>319100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>318100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>319400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>265100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>256700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>258200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>243100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>228700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>247500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>263700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>271200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>253600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>265100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>271800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>285700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>258700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>278800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>199100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>197400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>177900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>186100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>182800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>177700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>156100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>164200</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E45" s="3">
         <v>33000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>34100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>50000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>30300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>34100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>42900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>43300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>38300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>33000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>39100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>38800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>23700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>31200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>38400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>44800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>35800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>37800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>42900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>46800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>40200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>36300</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>38100</v>
       </c>
       <c r="Z45" s="3">
         <v>38100</v>
       </c>
       <c r="AA45" s="3">
+        <v>38100</v>
+      </c>
+      <c r="AB45" s="3">
         <v>23100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>24400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>24200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>26800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>33200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>583900</v>
+      </c>
+      <c r="E46" s="3">
         <v>585800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>581500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>611800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>617000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>603100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>626700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>583800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>572300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>535700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>546700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>517400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>495400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>515000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>533400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>533900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>548100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>564800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>582900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>564500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>558900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>600200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>460800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>441300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>430900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>422500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>410400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>401200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>470900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>438300</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3986,192 +4091,201 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>378700</v>
+      </c>
+      <c r="E48" s="3">
         <v>358000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>368700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>372100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>379600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>369500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>391300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>406100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>420400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>427700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>439600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>443200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>457000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>446400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>438300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>432400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>431600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>420000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>421800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>414000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>292900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>292600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>208000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>214700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>212600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>212300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>208700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>204400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>204500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>213600</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>161700</v>
+      </c>
+      <c r="E49" s="3">
         <v>156500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>162600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>162900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>162200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>174100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>193200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>212400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>223200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>230900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>240300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>239200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>253500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>240100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>226800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>219800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>346500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>343100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>353700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>334100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>343500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>353800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>67000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>70900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>68800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>68000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>66200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>63000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>61200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>65400</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4262,8 +4376,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4354,100 +4471,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>105900</v>
+      </c>
+      <c r="E52" s="3">
         <v>101300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>107200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>106500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>107700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>93900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>102200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>107500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>114200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>94900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>95600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>95500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>100000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>104200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>102500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>101000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>96800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>96700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>95900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>92500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>89300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>96300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>88800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>88600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>88300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>99600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>98700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>105000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>98800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4538,100 +4661,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1230100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1201600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1220000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1253200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1266500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1240600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1313400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1309800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1330100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1289200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1322200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1295300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1306000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1305800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1301000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1287100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1423000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1424500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1454300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1405100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1284600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1343000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>824600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>815500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>800600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>802400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>783900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>773700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>835400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>787500</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4664,8 +4793,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4698,168 +4828,172 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>62900</v>
+      </c>
+      <c r="E57" s="3">
         <v>75600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>69800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>85600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>78300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>83600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>92600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>87000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>85900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>72500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>82400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>72000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>58700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>63800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>64900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>68700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>75700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>72500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>67600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>73000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>66300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>69400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>61500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>55300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>50700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>52300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>49800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>48300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>45400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>48400</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E58" s="3">
         <v>10700</v>
-      </c>
-      <c r="E58" s="3">
-        <v>12400</v>
       </c>
       <c r="F58" s="3">
         <v>12400</v>
       </c>
       <c r="G58" s="3">
+        <v>12400</v>
+      </c>
+      <c r="H58" s="3">
         <v>12300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>16400</v>
-      </c>
-      <c r="I58" s="3">
-        <v>16700</v>
       </c>
       <c r="J58" s="3">
         <v>16700</v>
       </c>
       <c r="K58" s="3">
+        <v>16700</v>
+      </c>
+      <c r="L58" s="3">
         <v>16800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>16900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>17100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>16900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>16800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>32700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>32500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>32300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>32500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>32900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>32200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>32100</v>
-      </c>
-      <c r="W58" s="3">
-        <v>31300</v>
       </c>
       <c r="X58" s="3">
         <v>31300</v>
       </c>
       <c r="Y58" s="3">
-        <v>15000</v>
+        <v>31300</v>
       </c>
       <c r="Z58" s="3">
         <v>15000</v>
@@ -4882,376 +5016,391 @@
       <c r="AF58" s="3">
         <v>15000</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>140700</v>
+      </c>
+      <c r="E59" s="3">
         <v>123800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>112100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>123500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>129900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>137900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>140100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>142100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>159000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>145400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>130200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>128100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>117800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>148400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>135200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>129300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>155100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>149600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>134400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>127400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>126000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>137900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>103000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>99200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>111000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>101300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>92100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>92300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>98700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>90500</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>214700</v>
+      </c>
+      <c r="E60" s="3">
         <v>210200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>194300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>221500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>220500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>237900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>249400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>245900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>261800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>234800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>229600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>217100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>193300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>244800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>232600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>230300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>263300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>255000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>234300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>232500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>223600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>238500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>179500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>169600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>176600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>168700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>156900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>155600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>159100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>153900</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>413700</v>
+      </c>
+      <c r="E61" s="3">
         <v>440400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>469300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>495000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>514100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>510700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>534800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>509900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>506300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>513400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>545300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>550500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>563900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>551100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>590600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>597800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>566900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>595600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>642200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>611900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>587300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>617600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>228500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>228900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>214900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>219500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>215400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>208000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>255300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>202600</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>175800</v>
+      </c>
+      <c r="E62" s="3">
         <v>163500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>171500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>169700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>170400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>170700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>181900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>187200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>198600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>204200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>211700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>212900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>222200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>222800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>219600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>220300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>224700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>216600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>225700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>211000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>119100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>133900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>76000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>78600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>78900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>82000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>79700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>79000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>80300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>53600</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5342,8 +5491,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5434,8 +5586,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5526,100 +5681,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>804100</v>
+      </c>
+      <c r="E66" s="3">
         <v>814100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>835000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>886200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>905000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>919200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>966100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>942900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>966700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>952500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>986600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>980500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>979500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1018800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1042800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1048400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1054800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1067200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1102200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1055400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>930000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>990000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>484000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>477100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>470500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>470200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>452000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>442700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>494700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>410000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5652,8 +5813,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5744,8 +5906,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5836,8 +6001,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5928,8 +6096,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6020,100 +6191,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>320800</v>
+      </c>
+      <c r="E72" s="3">
         <v>301900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>292600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>277300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>278600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>303800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>290400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>274100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>261400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>240200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>229800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>214900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>208600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>189500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>184200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>180100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>286100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>273400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>251000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>225400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>222200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>219700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>215400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>198600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>187400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>183400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>168000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>150800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>140200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>139300</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6204,8 +6381,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6296,8 +6476,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6388,100 +6571,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>425900</v>
+      </c>
+      <c r="E76" s="3">
         <v>387600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>384900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>367000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>361500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>321400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>347400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>366900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>363400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>336800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>335600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>314800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>326500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>287000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>258200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>238700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>368200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>357400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>352100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>349700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>354700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>353000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>340600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>338400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>330100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>332200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>331900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>331000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>340700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>377500</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6572,197 +6761,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45200</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45109</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45018</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44927</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44836</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44745</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44654</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44563</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44472</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44381</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44290</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44199</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44108</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44017</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43926</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43828</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43737</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43464</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43282</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43191</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43009</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42918</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42827</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42736</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E81" s="3">
         <v>9800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>15600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-24200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>13800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>16500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>13100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>21800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>11000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>15500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>19600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-102200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>16400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>26200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>29500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>7100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>6400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>8200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>20600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>15100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>4300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>19400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>20900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>8500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>4700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6795,100 +6993,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E83" s="3">
         <v>11700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>11500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>11300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>10900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>11000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>11400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>12000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>12600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>12800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>13200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>13400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>13900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>13100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>12100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>12300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>12700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>13300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>15000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>12300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>8500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>8700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>8100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>7800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>6200</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>8200</v>
       </c>
       <c r="AE83" s="3">
         <v>8200</v>
       </c>
       <c r="AF83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AG83" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6979,8 +7181,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7071,8 +7276,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7163,8 +7371,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7255,8 +7466,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7347,100 +7561,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E89" s="3">
         <v>66300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>18300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>29600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>28200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>27600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-17700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>22600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>28900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>10300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>24900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>21800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>64800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>48100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-15700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>51900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>69500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>32100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-11700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>33100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>53700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>10800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>35400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>46000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>14600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>7400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>19200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>44300</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7473,100 +7693,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-10700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-16100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-22200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-20800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-19000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-15000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-20000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-26000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-12500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-8900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-7700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-8100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-15700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-16300</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7657,8 +7881,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7749,100 +7976,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-10700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-14600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-11400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-13400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-22300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-20400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-18900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-14900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-20000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-26700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-413200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-8700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-8200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-7400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-7600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-6700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-8600</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7875,8 +8108,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7884,55 +8118,55 @@
         <v>-600</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
         <v>-600</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
       <c r="K96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="L96" s="3">
         <v>-600</v>
       </c>
       <c r="M96" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
       <c r="O96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="P96" s="3">
         <v>-600</v>
       </c>
       <c r="Q96" s="3">
+        <v>-600</v>
+      </c>
+      <c r="R96" s="3">
         <v>-4400</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
-        <v>-3800</v>
+        <v>0</v>
       </c>
       <c r="T96" s="3">
         <v>-3800</v>
       </c>
       <c r="U96" s="3">
-        <v>-3900</v>
+        <v>-3800</v>
       </c>
       <c r="V96" s="3">
         <v>-3900</v>
@@ -7953,22 +8187,25 @@
         <v>-3900</v>
       </c>
       <c r="AB96" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-4000</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-3800</v>
       </c>
       <c r="AD96" s="3">
         <v>-3800</v>
       </c>
       <c r="AE96" s="3">
-        <v>-3900</v>
+        <v>-3800</v>
       </c>
       <c r="AF96" s="3">
         <v>-3900</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>-3900</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8059,8 +8296,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8151,8 +8391,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8243,280 +8486,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-30700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-31800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-28000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-21000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-9000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-32000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>18600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-7800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-31800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-8300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-13000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-12500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-45800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-16900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>32500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-36500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-47400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>17600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-31200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>400200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-19400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-28300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-22500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-86800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>42600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-11200</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-3700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>4700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-2200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>2700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E102" s="3">
         <v>26700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-8300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>18100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-12200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>15600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-21200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>4400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-9600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>11900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>19200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-8700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>17300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-14000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-26300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>40300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-19200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>8900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>11300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-13300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-85600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>51900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>25400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TILE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TILE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
   <si>
     <t>TILE</t>
   </si>
@@ -656,419 +656,432 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45200</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45109</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45018</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44927</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44836</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44745</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44654</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44563</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44472</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44381</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44290</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44199</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44108</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44017</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43926</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43828</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43737</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43464</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43282</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43191</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43009</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42918</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42827</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42736</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>289700</v>
+      </c>
+      <c r="E8" s="3">
         <v>325100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>311000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>329600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>295800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>335600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>327800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>346600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>288000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>339600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>312700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>294800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>253300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>276900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>278600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>259500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>288200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>339500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>348400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>357500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>297700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>337100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>318300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>283600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>240600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>266200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>257400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>251700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>221100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>239500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>248300</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>179300</v>
+      </c>
+      <c r="E9" s="3">
         <v>202000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>200700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>217800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>199900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>230100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>219000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>229900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>181200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>218300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>206400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>185800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>157200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>180100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>176500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>162200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>173900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>196300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>212600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>216800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>181200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>215400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>218400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>174500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>147000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>164400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>158900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>153800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>133300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>149500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>155400</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>110400</v>
+      </c>
+      <c r="E10" s="3">
         <v>123100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>110300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>111800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>95900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>105500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>108800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>116700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>106800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>121300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>106300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>109000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>96100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>96800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>102100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>97300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>114300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>143200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>135800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>140700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>116500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>121700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>99900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>109100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>93600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>101800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>98500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>97900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>87800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>90000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>92900</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1102,8 +1115,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1197,8 +1211,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1292,8 +1309,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1304,65 +1324,65 @@
         <v>0</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>-2600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>36600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-1900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>120100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>12300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>700</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>20500</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
@@ -1379,16 +1399,19 @@
         <v>0</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>7300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>19800</v>
       </c>
-      <c r="AG14" s="3" t="s">
+      <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1482,8 +1505,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1514,198 +1540,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>265300</v>
+      </c>
+      <c r="E17" s="3">
         <v>290000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>280000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>300700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>286300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>350100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>299700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>312100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>260600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>305700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>287900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>265600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>236400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>256000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>262800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>242100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>381700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>311500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>304700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>314600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>281300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>333200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>302500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>249900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>217600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>235300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>226100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>218200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>205300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>233100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>222600</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E18" s="3">
         <v>35100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>31000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>28900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>9500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-14500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>28100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>34500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>27400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>33900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>24800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>29200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>16900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>20900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>15800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>17400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-93500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>28000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>43700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>42900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>16400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>15800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>33700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>23000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>31000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>31300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>33500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>15800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>6400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>25700</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1739,483 +1772,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-6700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-200</v>
       </c>
       <c r="L20" s="3">
         <v>-200</v>
       </c>
       <c r="M20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N20" s="3">
         <v>-900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1500</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-1100</v>
       </c>
       <c r="U20" s="3">
         <v>-1100</v>
       </c>
       <c r="V20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="W20" s="3">
         <v>-300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>36300</v>
+      </c>
+      <c r="E21" s="3">
         <v>45200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>36000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>40900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>19300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-5600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>38900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>44600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>39300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>46300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>36700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>41800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>29500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>33500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>26100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>24400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-82700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>39500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>54900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>55300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>28600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>18300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>26500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>38900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>31200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>38300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>38000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>40300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>21400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>15900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>32500</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E22" s="3">
         <v>6800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>8200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>8300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>8500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>8100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>7200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>6900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>7700</v>
-      </c>
-      <c r="N22" s="3">
-        <v>7300</v>
       </c>
       <c r="O22" s="3">
         <v>7300</v>
       </c>
       <c r="P22" s="3">
+        <v>7300</v>
+      </c>
+      <c r="Q22" s="3">
         <v>13200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>5400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>5000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>5600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>5500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>6600</v>
-      </c>
-      <c r="V22" s="3">
-        <v>6800</v>
       </c>
       <c r="W22" s="3">
         <v>6800</v>
       </c>
       <c r="X22" s="3">
+        <v>6800</v>
+      </c>
+      <c r="Y22" s="3">
         <v>6200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>4900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E23" s="3">
         <v>26900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>16100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>21100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-24600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>20200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>25900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>20400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>26300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>16200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>21300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-100600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>21400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>36100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>35800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>8600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>9400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>28200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>20400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>28200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>28400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>31100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>12800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>6400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E24" s="3">
         <v>7400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>6100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>9100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>9900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>8700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>9000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>10200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>7400</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2309,198 +2358,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E26" s="3">
         <v>19600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>9900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>15800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-24600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>14100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>16800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>13300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>21800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>11000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>15500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>19600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-102200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>16400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>26200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>29500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>7100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>8200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>20600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>15100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>19500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>19400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>20900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>8500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>4700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E27" s="3">
         <v>19300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>9800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>15600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-24200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>13800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>16500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>13100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>21800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>11000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>15500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>19600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-102200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>16400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>26200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>29500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>7100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>8200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>20600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>15100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>19500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>19400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>20900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>8500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>4700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2594,8 +2652,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2638,8 +2699,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
@@ -2659,11 +2720,11 @@
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
         <v>6700</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2671,11 +2732,11 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-15200</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2689,8 +2750,11 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2784,8 +2848,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2879,198 +2946,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E32" s="3">
         <v>1400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>6700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1400</v>
-      </c>
-      <c r="K32" s="3">
-        <v>200</v>
       </c>
       <c r="L32" s="3">
         <v>200</v>
       </c>
       <c r="M32" s="3">
+        <v>200</v>
+      </c>
+      <c r="N32" s="3">
         <v>900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1500</v>
-      </c>
-      <c r="T32" s="3">
-        <v>1100</v>
       </c>
       <c r="U32" s="3">
         <v>1100</v>
       </c>
       <c r="V32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="W32" s="3">
         <v>300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E33" s="3">
         <v>19300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>9800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>15600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-24200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>13800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>16500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>13100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>21800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>11000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>15500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>19600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-102200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>16400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>26200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>29500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>7100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>6400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>8200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>20600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>15100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>4300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>19400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>20900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>8500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>4700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3164,203 +3240,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E35" s="3">
         <v>19300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>9800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>15600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-24200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>13800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>16500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>13100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>21800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>11000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>15500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>19600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-102200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>16400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>26200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>29500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>7100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>6400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>8200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>20600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>15100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>4300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>19400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>20900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>8500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>4700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45200</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45109</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45018</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44927</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44836</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44745</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44654</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44563</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44472</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44381</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44290</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44199</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44108</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44017</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43926</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43828</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43737</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43464</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43282</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43191</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43009</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42918</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42827</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42736</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3394,8 +3479,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3429,103 +3515,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>89800</v>
+      </c>
+      <c r="E41" s="3">
         <v>110500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>119600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>92900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>101300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>97600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>79400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>91700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>76100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>97300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>92800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>102400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>106900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>103100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>103700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>91800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>72700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>81300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>85200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>84300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>67000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>81000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>107300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>67000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>67900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>87000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>78100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>66800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>80000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>165700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>113700</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3619,388 +3709,403 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>147200</v>
+      </c>
+      <c r="E43" s="3">
         <v>163400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>143900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>166300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>147800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>182800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>170400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>174000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>145000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>171700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>153200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>146900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>128600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>139900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>132600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>139400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>145300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>177500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>176700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>183900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>165000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>179000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>177800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>156600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>137900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>142800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>133900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>136600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>116700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>126000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>128700</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>296200</v>
+      </c>
+      <c r="E44" s="3">
         <v>279100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>289300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>288200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>312700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>306300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>319100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>318100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>319400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>265100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>256700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>258200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>243100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>228700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>247500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>263700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>271200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>253600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>265100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>271800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>285700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>258700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>278800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>199100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>197400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>177900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>186100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>182800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>177700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>156100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>164200</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E45" s="3">
         <v>30900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>33000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>34100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>50000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>30300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>34100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>42900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>43300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>38300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>33000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>39100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>38800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>23700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>31200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>38400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>44800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>35800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>37800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>42900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>46800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>40200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>36300</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>38100</v>
       </c>
       <c r="AA45" s="3">
         <v>38100</v>
       </c>
       <c r="AB45" s="3">
+        <v>38100</v>
+      </c>
+      <c r="AC45" s="3">
         <v>23100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>24400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>24200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>26800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>33200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>566100</v>
+      </c>
+      <c r="E46" s="3">
         <v>583900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>585800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>581500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>611800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>617000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>603100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>626700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>583800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>572300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>535700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>546700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>517400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>495400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>515000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>533400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>533900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>548100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>564800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>582900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>564500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>558900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>600200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>460800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>441300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>430900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>422500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>410400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>401200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>470900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>438300</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4094,198 +4199,207 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>364100</v>
+      </c>
+      <c r="E48" s="3">
         <v>378700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>358000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>368700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>372100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>379600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>369500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>391300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>406100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>420400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>427700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>439600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>443200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>457000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>446400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>438300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>432400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>431600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>420000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>421800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>414000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>292900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>292600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>208000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>214700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>212600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>212300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>208700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>204400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>204500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>213600</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>157000</v>
+      </c>
+      <c r="E49" s="3">
         <v>161700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>156500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>162600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>162900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>162200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>174100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>193200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>212400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>223200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>230900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>240300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>239200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>253500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>240100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>226800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>219800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>346500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>343100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>353700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>334100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>343500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>353800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>67000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>70900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>68800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>68000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>66200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>63000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>61200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>65400</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4379,8 +4493,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4474,103 +4591,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>106400</v>
+      </c>
+      <c r="E52" s="3">
         <v>105900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>101300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>107200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>106500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>107700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>93900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>102200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>107500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>114200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>94900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>95600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>95500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>100000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>104200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>102500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>101000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>96800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>96700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>95900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>92500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>89300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>96300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>88800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>88600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>88300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>99600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>98700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>105000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>98800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4664,103 +4787,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1193500</v>
+      </c>
+      <c r="E54" s="3">
         <v>1230100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1201600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1220000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1253200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1266500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1240600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1313400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1309800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1330100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1289200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1322200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1295300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1306000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1305800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1301000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1287100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1423000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1424500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1454300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1405100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1284600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1343000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>824600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>815500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>800600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>802400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>783900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>773700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>835400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>787500</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4794,8 +4923,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4829,174 +4959,178 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>74500</v>
+      </c>
+      <c r="E57" s="3">
         <v>62900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>75600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>69800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>85600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>78300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>83600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>92600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>87000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>85900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>72500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>82400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>72000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>58700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>63800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>64900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>68700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>75700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>72500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>67600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>73000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>66300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>69400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>61500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>55300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>50700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>52300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>49800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>48300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>45400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>48400</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E58" s="3">
         <v>11200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10700</v>
-      </c>
-      <c r="F58" s="3">
-        <v>12400</v>
       </c>
       <c r="G58" s="3">
         <v>12400</v>
       </c>
       <c r="H58" s="3">
+        <v>12400</v>
+      </c>
+      <c r="I58" s="3">
         <v>12300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>16400</v>
-      </c>
-      <c r="J58" s="3">
-        <v>16700</v>
       </c>
       <c r="K58" s="3">
         <v>16700</v>
       </c>
       <c r="L58" s="3">
+        <v>16700</v>
+      </c>
+      <c r="M58" s="3">
         <v>16800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>16900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>17100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>16900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>16800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>32700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>32500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>32300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>32500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>32900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>32200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>32100</v>
-      </c>
-      <c r="X58" s="3">
-        <v>31300</v>
       </c>
       <c r="Y58" s="3">
         <v>31300</v>
       </c>
       <c r="Z58" s="3">
-        <v>15000</v>
+        <v>31300</v>
       </c>
       <c r="AA58" s="3">
         <v>15000</v>
@@ -5019,388 +5153,403 @@
       <c r="AG58" s="3">
         <v>15000</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>122200</v>
+      </c>
+      <c r="E59" s="3">
         <v>140700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>123800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>112100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>123500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>129900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>137900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>140100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>142100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>159000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>145400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>130200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>128100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>117800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>148400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>135200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>129300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>155100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>149600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>134400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>127400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>126000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>137900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>103000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>99200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>111000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>101300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>92100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>92300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>98700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>90500</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>207700</v>
+      </c>
+      <c r="E60" s="3">
         <v>214700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>210200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>194300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>221500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>220500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>237900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>249400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>245900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>261800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>234800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>229600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>217100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>193300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>244800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>232600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>230300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>263300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>255000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>234300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>232500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>223600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>238500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>179500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>169600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>176600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>168700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>156900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>155600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>159100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>153900</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>388000</v>
+      </c>
+      <c r="E61" s="3">
         <v>413700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>440400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>469300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>495000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>514100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>510700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>534800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>509900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>506300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>513400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>545300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>550500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>563900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>551100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>590600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>597800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>566900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>595600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>642200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>611900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>587300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>617600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>228500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>228900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>214900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>219500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>215400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>208000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>255300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>202600</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>169300</v>
+      </c>
+      <c r="E62" s="3">
         <v>175800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>163500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>171500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>169700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>170400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>170700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>181900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>187200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>198600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>204200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>211700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>212900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>222200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>222800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>219600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>220300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>224700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>216600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>225700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>211000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>119100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>133900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>76000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>78600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>78900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>82000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>79700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>79000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>80300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>53600</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5494,8 +5643,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5589,8 +5741,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5684,103 +5839,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>764900</v>
+      </c>
+      <c r="E66" s="3">
         <v>804100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>814100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>835000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>886200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>905000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>919200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>966100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>942900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>966700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>952500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>986600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>980500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>979500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1018800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1042800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1048400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1054800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1067200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1102200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1055400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>930000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>990000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>484000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>477100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>470500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>470200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>452000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>442700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>494700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>410000</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5814,8 +5975,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5909,8 +6071,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6004,8 +6169,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6099,8 +6267,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6194,103 +6365,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>334400</v>
+      </c>
+      <c r="E72" s="3">
         <v>320800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>301900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>292600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>277300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>278600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>303800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>290400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>274100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>261400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>240200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>229800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>214900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>208600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>189500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>184200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>180100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>286100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>273400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>251000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>225400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>222200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>219700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>215400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>198600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>187400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>183400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>168000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>150800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>140200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>139300</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6384,8 +6561,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6479,8 +6659,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6574,103 +6757,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>428500</v>
+      </c>
+      <c r="E76" s="3">
         <v>425900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>387600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>384900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>367000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>361500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>321400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>347400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>366900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>363400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>336800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>335600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>314800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>326500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>287000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>258200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>238700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>368200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>357400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>352100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>349700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>354700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>353000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>340600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>338400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>330100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>332200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>331900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>331000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>340700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>377500</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6764,203 +6953,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45200</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45109</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45018</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44927</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44836</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44745</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44654</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44563</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44472</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44381</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44290</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44199</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44108</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44017</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43926</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43828</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43737</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43464</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43282</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43191</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43009</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42918</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42827</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42736</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E81" s="3">
         <v>19300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>9800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>15600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-24200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>13800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>16500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>13100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>21800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>11000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>15500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>19600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-102200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>16400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>26200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>29500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>7100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>6400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>8200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>20600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>15100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>4300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>19400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>20900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>8500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>4700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6994,103 +7192,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E83" s="3">
         <v>11500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>11700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>11500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>11300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>10900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>11000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>11400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>12000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>12600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>12800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>13200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>13400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>13900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>13100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>12100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>12300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>12700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>13300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>15000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>12300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>8500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>8700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>8100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>7800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>6200</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>8200</v>
       </c>
       <c r="AF83" s="3">
         <v>8200</v>
       </c>
       <c r="AG83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AH83" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7184,8 +7386,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7279,8 +7484,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7374,8 +7582,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7469,8 +7680,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7564,103 +7778,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E89" s="3">
         <v>27800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>66300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>18300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>29600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>28200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>27600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-17700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>22600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>28900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>10300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>24900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>21800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>64800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>48100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-15700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>51900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>69500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>32100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-11700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>33100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>53700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>10800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-5800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>35400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>46000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>14600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>7400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>19200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>44300</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7694,103 +7914,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-10700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-11200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-22200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-20800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-19000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-15000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-20000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-26000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-12500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-8900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-7700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-7500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-8100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-15700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-16300</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7884,8 +8108,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7979,103 +8206,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-8900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-10700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-14600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-11400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-13400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-22300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-20400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-18900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-14900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-20000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-26700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-413200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-8700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-8200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-7400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-7600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-6700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-8600</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8109,67 +8342,68 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
         <v>-600</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
         <v>-600</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
       <c r="L96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="M96" s="3">
         <v>-600</v>
       </c>
       <c r="N96" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
       <c r="P96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="Q96" s="3">
         <v>-600</v>
       </c>
       <c r="R96" s="3">
+        <v>-600</v>
+      </c>
+      <c r="S96" s="3">
         <v>-4400</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
-        <v>-3800</v>
+        <v>0</v>
       </c>
       <c r="U96" s="3">
         <v>-3800</v>
       </c>
       <c r="V96" s="3">
-        <v>-3900</v>
+        <v>-3800</v>
       </c>
       <c r="W96" s="3">
         <v>-3900</v>
@@ -8190,22 +8424,25 @@
         <v>-3900</v>
       </c>
       <c r="AC96" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-4000</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-3800</v>
       </c>
       <c r="AE96" s="3">
         <v>-3800</v>
       </c>
       <c r="AF96" s="3">
-        <v>-3900</v>
+        <v>-3800</v>
       </c>
       <c r="AG96" s="3">
         <v>-3900</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>-3900</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8299,8 +8536,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8394,8 +8634,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8489,289 +8732,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-29800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-30700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-31800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-28000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-21000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-9000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-32000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>18600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-7800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-31800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-8300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-13000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-12500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-45800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-16900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>32500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-36500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-47400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>17600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-31200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>400200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-5800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-19400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-28300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-22500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-86800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>42600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-11200</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E101" s="3">
         <v>2600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>4100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-3600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>4200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-3100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>2700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-9100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>26700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-8300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>18100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-12200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>15600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-21200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-9600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>11900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>19200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-8700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>17300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-14000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-26300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>40300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-19200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>8900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>11300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-13300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-85600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>51900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>25400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TILE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TILE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
   <si>
     <t>TILE</t>
   </si>
@@ -656,432 +656,445 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45200</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45109</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45018</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44927</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44836</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44745</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44654</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44563</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44472</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44381</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44290</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44199</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44108</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44017</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43926</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43828</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43737</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43464</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43282</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43191</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43009</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42918</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42827</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42736</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>346600</v>
+      </c>
+      <c r="E8" s="3">
         <v>289700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>325100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>311000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>329600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>295800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>335600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>327800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>346600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>288000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>339600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>312700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>294800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>253300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>276900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>278600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>259500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>288200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>339500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>348400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>357500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>297700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>337100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>318300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>283600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>240600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>266200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>257400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>251700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>221100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>239500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>248300</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>224000</v>
+      </c>
+      <c r="E9" s="3">
         <v>179300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>202000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>200700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>217800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>199900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>230100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>219000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>229900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>181200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>218300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>206400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>185800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>157200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>180100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>176500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>162200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>173900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>196300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>212600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>216800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>181200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>215400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>218400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>174500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>147000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>164400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>158900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>153800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>133300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>149500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>155400</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>122600</v>
+      </c>
+      <c r="E10" s="3">
         <v>110400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>123100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>110300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>111800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>95900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>105500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>108800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>116700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>106800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>121300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>106300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>109000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>96100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>96800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>102100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>97300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>114300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>143200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>135800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>140700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>116500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>121700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>99900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>109100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>93600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>101800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>98500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>97900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>87800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>90000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>92900</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1116,8 +1129,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1214,8 +1228,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1312,8 +1329,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1327,65 +1347,65 @@
         <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>-2600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>36600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-1500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-1900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>120100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>12300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>700</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>20500</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
@@ -1402,16 +1422,19 @@
         <v>0</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>7300</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>19800</v>
       </c>
-      <c r="AH14" s="3" t="s">
+      <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1508,8 +1531,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1541,204 +1567,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>308500</v>
+      </c>
+      <c r="E17" s="3">
         <v>265300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>290000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>280000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>300700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>286300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>350100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>299700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>312100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>260600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>305700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>287900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>265600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>236400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>256000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>262800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>242100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>381700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>311500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>304700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>314600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>281300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>333200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>302500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>249900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>217600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>235300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>226100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>218200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>205300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>233100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>222600</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E18" s="3">
         <v>24400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>35100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>31000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>28900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>9500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-14500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>28100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>34500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>27400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>33900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>24800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>29200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>16900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>20900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>15800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>17400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-93500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>28000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>43700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>42900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>16400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>15800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>33700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>23000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>31000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>31300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>33500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>15800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>6400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>25700</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1773,498 +1806,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E20" s="3">
         <v>1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-6700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-200</v>
       </c>
       <c r="M20" s="3">
         <v>-200</v>
       </c>
       <c r="N20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O20" s="3">
         <v>-900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-5100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1500</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-1100</v>
       </c>
       <c r="V20" s="3">
         <v>-1100</v>
       </c>
       <c r="W20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="X20" s="3">
         <v>-300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>48300</v>
+      </c>
+      <c r="E21" s="3">
         <v>36300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>45200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>36000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>40900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>19300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-5600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>38900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>44600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>39300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>46300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>36700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>41800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>29500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>33500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>26100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>24400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-82700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>39500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>54900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>55300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>28600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>18300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>26500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>38900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>31200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>38300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>38000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>40300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>21400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>15900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>32500</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E22" s="3">
         <v>6400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>8200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>8300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>8500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>8100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>7700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>6900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>7400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>7700</v>
-      </c>
-      <c r="O22" s="3">
-        <v>7300</v>
       </c>
       <c r="P22" s="3">
         <v>7300</v>
       </c>
       <c r="Q22" s="3">
+        <v>7300</v>
+      </c>
+      <c r="R22" s="3">
         <v>13200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>5400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>5000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>5600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>5500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>6600</v>
-      </c>
-      <c r="W22" s="3">
-        <v>6800</v>
       </c>
       <c r="X22" s="3">
         <v>6800</v>
       </c>
       <c r="Y22" s="3">
+        <v>6800</v>
+      </c>
+      <c r="Z22" s="3">
         <v>6200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>4900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>1400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E23" s="3">
         <v>19000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>26900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>16100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>21100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-24600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>20200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>25900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>20400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>26300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>16200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>21300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-100600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>21400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>36100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>35800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>8600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>9400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>28200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>20400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>28200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>28400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>31100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>12800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>6400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E24" s="3">
         <v>4800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>6100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>9100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-13200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>4900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>9900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>6300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>7600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>5300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>8700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>9000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>10200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>4200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>7400</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2361,204 +2410,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E26" s="3">
         <v>14200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>19600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>9900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>15800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-24600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>14100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>16800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>13300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>21800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>11000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>15500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>19600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-102200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>16400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>26200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>29500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>7100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>8200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>20600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>15100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>19500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>19400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>20900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>8500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>4700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E27" s="3">
         <v>14000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>19300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>9800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>15600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-24200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>13800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>16500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>13100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>21800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>11000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>15500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>19600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-102200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>16400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>26200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>29500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>7100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>8200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>20600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>15100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>19500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>19400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>20900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>8500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>4700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2655,8 +2713,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2702,8 +2763,8 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
@@ -2723,11 +2784,11 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>6700</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2735,11 +2796,11 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-15200</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2753,8 +2814,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2851,8 +2915,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2949,204 +3016,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>6700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1400</v>
-      </c>
-      <c r="L32" s="3">
-        <v>200</v>
       </c>
       <c r="M32" s="3">
         <v>200</v>
       </c>
       <c r="N32" s="3">
+        <v>200</v>
+      </c>
+      <c r="O32" s="3">
         <v>900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>5100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1500</v>
-      </c>
-      <c r="U32" s="3">
-        <v>1100</v>
       </c>
       <c r="V32" s="3">
         <v>1100</v>
       </c>
       <c r="W32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X32" s="3">
         <v>300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E33" s="3">
         <v>14000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>19300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>9800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>15600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-24200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>13800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>16500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>13100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>21800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>11000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>15500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>19600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-102200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>16400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>26200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>29500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>7100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>6400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>8200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>20600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>15100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>4300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>19400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>20900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>8500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>4700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3243,209 +3319,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E35" s="3">
         <v>14000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>19300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>9800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>15600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-24200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>13800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>16500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>13100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>21800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>11000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>15500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>19600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-102200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>16400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>26200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>29500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>7100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>6400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>8200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>20600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>15100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>4300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>19400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>20900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>8500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>4700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45200</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45109</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45018</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44927</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44836</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44745</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44654</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44563</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44472</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44381</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44290</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44199</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44108</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44017</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43926</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43828</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43737</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43464</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43282</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43191</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43009</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42918</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42827</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42736</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3480,8 +3565,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3516,106 +3602,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>94200</v>
+      </c>
+      <c r="E41" s="3">
         <v>89800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>110500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>119600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>92900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>101300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>97600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>79400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>91700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>76100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>97300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>92800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>102400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>106900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>103100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>103700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>91800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>72700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>81300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>85200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>84300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>67000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>81000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>107300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>67000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>67900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>87000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>78100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>66800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>80000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>165700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>113700</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3712,400 +3802,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>179600</v>
+      </c>
+      <c r="E43" s="3">
         <v>147200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>163400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>143900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>166300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>147800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>182800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>170400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>174000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>145000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>171700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>153200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>146900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>128600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>139900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>132600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>139400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>145300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>177500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>176700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>183900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>165000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>179000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>177800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>156600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>137900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>142800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>133900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>136600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>116700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>126000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>128700</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>281100</v>
+      </c>
+      <c r="E44" s="3">
         <v>296200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>279100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>289300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>288200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>312700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>306300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>319100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>318100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>319400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>265100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>256700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>258200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>243100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>228700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>247500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>263700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>271200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>253600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>265100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>271800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>285700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>258700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>278800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>199100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>197400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>177900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>186100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>182800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>177700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>156100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>164200</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E45" s="3">
         <v>32900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>30900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>33000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>34100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>50000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>30300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>34100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>42900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>43300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>38300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>33000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>39100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>38800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>23700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>31200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>38400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>44800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>35800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>37800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>42900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>46800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>40200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>36300</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>38100</v>
       </c>
       <c r="AB45" s="3">
         <v>38100</v>
       </c>
       <c r="AC45" s="3">
+        <v>38100</v>
+      </c>
+      <c r="AD45" s="3">
         <v>23100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>24400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>24200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>26800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>33200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>591800</v>
+      </c>
+      <c r="E46" s="3">
         <v>566100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>583900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>585800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>581500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>611800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>617000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>603100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>626700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>583800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>572300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>535700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>546700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>517400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>495400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>515000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>533400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>533900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>548100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>564800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>582900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>564500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>558900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>600200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>460800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>441300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>430900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>422500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>410400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>401200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>470900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>438300</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4202,204 +4307,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>362400</v>
+      </c>
+      <c r="E48" s="3">
         <v>364100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>378700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>358000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>368700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>372100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>379600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>369500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>391300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>406100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>420400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>427700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>439600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>443200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>457000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>446400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>438300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>432400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>431600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>420000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>421800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>414000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>292900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>292600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>208000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>214700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>212600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>212300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>208700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>204400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>204500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>213600</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>154600</v>
+      </c>
+      <c r="E49" s="3">
         <v>157000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>161700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>156500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>162600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>162900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>162200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>174100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>193200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>212400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>223200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>230900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>240300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>239200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>253500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>240100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>226800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>219800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>346500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>343100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>353700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>334100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>343500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>353800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>67000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>70900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>68800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>68000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>66200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>63000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>61200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>65400</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4496,8 +4610,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4594,106 +4711,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>107300</v>
+      </c>
+      <c r="E52" s="3">
         <v>106400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>105900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>101300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>107200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>106500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>107700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>93900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>102200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>107500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>114200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>94900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>95600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>95500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>100000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>104200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>102500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>101000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>96800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>96700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>95900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>92500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>89300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>96300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>88800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>88600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>88300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>99600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>98700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>105000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>98800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4790,106 +4913,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1216100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1193500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1230100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1201600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1220000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1253200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1266500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1240600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1313400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1309800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1330100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1289200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1322200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1295300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1306000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1305800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1301000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1287100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1423000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1424500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1454300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1405100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1284600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1343000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>824600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>815500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>800600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>802400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>783900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>773700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>835400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>787500</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4924,8 +5053,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4960,180 +5090,184 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>78500</v>
+      </c>
+      <c r="E57" s="3">
         <v>74500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>62900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>75600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>69800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>85600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>78300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>83600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>92600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>87000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>85900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>72500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>82400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>72000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>58700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>63800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>64900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>68700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>75700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>72500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>67600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>73000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>66300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>69400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>61500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>55300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>50700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>52300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>49800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>48300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>45400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>48400</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E58" s="3">
         <v>11000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10700</v>
-      </c>
-      <c r="G58" s="3">
-        <v>12400</v>
       </c>
       <c r="H58" s="3">
         <v>12400</v>
       </c>
       <c r="I58" s="3">
+        <v>12400</v>
+      </c>
+      <c r="J58" s="3">
         <v>12300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>16400</v>
-      </c>
-      <c r="K58" s="3">
-        <v>16700</v>
       </c>
       <c r="L58" s="3">
         <v>16700</v>
       </c>
       <c r="M58" s="3">
+        <v>16700</v>
+      </c>
+      <c r="N58" s="3">
         <v>16800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>16900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>17100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>16900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>16800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>32700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>32500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>32300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>32500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>32900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>32200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>32100</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>31300</v>
       </c>
       <c r="Z58" s="3">
         <v>31300</v>
       </c>
       <c r="AA58" s="3">
-        <v>15000</v>
+        <v>31300</v>
       </c>
       <c r="AB58" s="3">
         <v>15000</v>
@@ -5156,400 +5290,415 @@
       <c r="AH58" s="3">
         <v>15000</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>125100</v>
+      </c>
+      <c r="E59" s="3">
         <v>122200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>140700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>123800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>112100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>123500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>129900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>137900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>140100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>142100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>159000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>145400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>130200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>128100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>117800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>148400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>135200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>129300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>155100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>149600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>134400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>127400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>126000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>137900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>103000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>99200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>111000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>101300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>92100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>92300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>98700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>90500</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>214700</v>
+      </c>
+      <c r="E60" s="3">
         <v>207700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>214700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>210200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>194300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>221500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>220500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>237900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>249400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>245900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>261800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>234800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>229600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>217100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>193300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>244800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>232600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>230300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>263300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>255000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>234300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>232500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>223600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>238500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>179500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>169600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>176600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>168700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>156900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>155600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>159100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>153900</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>384100</v>
+      </c>
+      <c r="E61" s="3">
         <v>388000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>413700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>440400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>469300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>495000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>514100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>510700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>534800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>509900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>506300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>513400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>545300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>550500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>563900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>551100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>590600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>597800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>566900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>595600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>642200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>611900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>587300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>617600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>228500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>228900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>214900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>219500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>215400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>208000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>255300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>202600</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>166100</v>
+      </c>
+      <c r="E62" s="3">
         <v>169300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>175800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>163500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>171500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>169700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>170400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>170700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>181900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>187200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>198600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>204200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>211700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>212900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>222200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>222800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>219600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>220300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>224700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>216600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>225700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>211000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>119100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>133900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>76000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>78600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>78900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>82000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>79700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>79000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>80300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>53600</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5646,8 +5795,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5744,8 +5896,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5842,106 +5997,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>765000</v>
+      </c>
+      <c r="E66" s="3">
         <v>764900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>804100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>814100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>835000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>886200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>905000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>919200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>966100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>942900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>966700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>952500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>986600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>980500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>979500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1018800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1042800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1048400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1054800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1067200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1102200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1055400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>930000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>990000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>484000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>477100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>470500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>470200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>452000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>442700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>494700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>410000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5976,8 +6137,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6074,8 +6236,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6172,8 +6337,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6270,8 +6438,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6368,106 +6539,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>356400</v>
+      </c>
+      <c r="E72" s="3">
         <v>334400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>320800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>301900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>292600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>277300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>278600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>303800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>290400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>274100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>261400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>240200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>229800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>214900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>208600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>189500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>184200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>180100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>286100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>273400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>251000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>225400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>222200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>219700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>215400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>198600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>187400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>183400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>168000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>150800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>140200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>139300</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6564,8 +6741,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6662,8 +6842,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6760,106 +6943,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>451200</v>
+      </c>
+      <c r="E76" s="3">
         <v>428500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>425900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>387600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>384900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>367000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>361500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>321400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>347400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>366900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>363400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>336800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>335600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>314800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>326500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>287000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>258200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>238700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>368200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>357400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>352100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>349700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>354700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>353000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>340600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>338400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>330100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>332200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>331900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>331000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>340700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>377500</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6956,209 +7145,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45200</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45109</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45018</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44927</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44836</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44745</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44654</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44563</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44472</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44381</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44290</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44199</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44108</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44017</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43926</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43828</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43737</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43464</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43282</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43191</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43009</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42918</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42827</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42736</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E81" s="3">
         <v>14000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>19300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>9800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>15600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-24200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>13800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>16500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>13100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>21800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>11000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>15500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>19600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-102200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>16400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>26200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>29500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>7100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>6400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>8200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>20600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>15100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>4300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>19400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>20900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>8500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>4700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7193,106 +7391,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E83" s="3">
         <v>10900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>11500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>11700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>11500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>11300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>10900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>11000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>11400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>12000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>12600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>12800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>13200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>13400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>13900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>13100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>12100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>12200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>12700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>13300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>15000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>12300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>8500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>8700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>8100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>7800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>6200</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>8200</v>
       </c>
       <c r="AG83" s="3">
         <v>8200</v>
       </c>
       <c r="AH83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AI83" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7389,8 +7591,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7487,8 +7692,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7585,8 +7793,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7683,8 +7894,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7781,106 +7995,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E89" s="3">
         <v>12600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>27800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>66300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>18300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>29600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>28200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>27600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-17700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>22600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>28900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>10300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>24900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>21800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>64800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>48100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-15700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>51900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>69500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>32100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-11700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>33100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>53700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>10800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-5800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>35400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>46000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>14600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>7400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>19200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>44300</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7915,106 +8135,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-16100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-11200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-13500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-22200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-20800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-19000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-15000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-20000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-26000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-12500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-8900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-7700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-7500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-8100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-15700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-16300</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8111,8 +8335,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8209,106 +8436,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-10700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-14600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-11400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-13400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-22300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-20400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-18900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-14900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-20000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-26700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-413200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-8700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-8200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-7400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-7600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-6700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-8600</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8343,70 +8576,71 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-1200</v>
       </c>
       <c r="E96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
         <v>-600</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
         <v>-600</v>
       </c>
       <c r="K96" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
       <c r="M96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="N96" s="3">
         <v>-600</v>
       </c>
       <c r="O96" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
       <c r="Q96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="R96" s="3">
         <v>-600</v>
       </c>
       <c r="S96" s="3">
+        <v>-600</v>
+      </c>
+      <c r="T96" s="3">
         <v>-4400</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
-        <v>-3800</v>
+        <v>0</v>
       </c>
       <c r="V96" s="3">
         <v>-3800</v>
       </c>
       <c r="W96" s="3">
-        <v>-3900</v>
+        <v>-3800</v>
       </c>
       <c r="X96" s="3">
         <v>-3900</v>
@@ -8427,22 +8661,25 @@
         <v>-3900</v>
       </c>
       <c r="AD96" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-4000</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-3800</v>
       </c>
       <c r="AF96" s="3">
         <v>-3800</v>
       </c>
       <c r="AG96" s="3">
-        <v>-3900</v>
+        <v>-3800</v>
       </c>
       <c r="AH96" s="3">
         <v>-3900</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>-3900</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8539,8 +8776,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8637,8 +8877,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8735,298 +8978,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-29800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-30700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-31800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-28000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-21000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-9000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-32000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>18600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-7800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-31800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-8300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-12500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-45800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-16900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>32500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-36500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-47400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>17600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-31200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>400200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-5800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-19400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-28300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-22500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-86800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>42600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-11200</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>4100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>4700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>4200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-3100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>2700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-20700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-9100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>26700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>18100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-12200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>15600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-21200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-9600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>11900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>19200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-8700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>17300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-14000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-26300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>40300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-19200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>8900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>11300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-13300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-85600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>51900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>25400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TILE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TILE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
   <si>
     <t>TILE</t>
   </si>
@@ -656,445 +656,458 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45564</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45200</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45109</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45018</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44927</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44836</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44745</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44654</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44563</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44472</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44381</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44290</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44199</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44108</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44017</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43926</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43828</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43737</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43464</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43282</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43191</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43009</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42918</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42827</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42736</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>344300</v>
+      </c>
+      <c r="E8" s="3">
         <v>346600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>289700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>325100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>311000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>329600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>295800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>335600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>327800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>346600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>288000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>339600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>312700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>294800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>253300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>276900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>278600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>259500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>288200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>339500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>348400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>357500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>297700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>337100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>318300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>283600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>240600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>266200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>257400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>251700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>221100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>239500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>248300</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>216600</v>
+      </c>
+      <c r="E9" s="3">
         <v>224000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>179300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>202000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>200700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>217800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>199900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>230100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>219000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>229900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>181200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>218300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>206400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>185800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>157200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>180100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>176500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>162200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>173900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>196300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>212600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>216800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>181200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>215400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>218400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>174500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>147000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>164400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>158900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>153800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>133300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>149500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>155400</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>127600</v>
+      </c>
+      <c r="E10" s="3">
         <v>122600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>110400</v>
       </c>
-      <c r="F10" s="3">
-        <v>123100</v>
-      </c>
       <c r="G10" s="3">
+        <v>123200</v>
+      </c>
+      <c r="H10" s="3">
         <v>110300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>111800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>95900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>105500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>108800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>116700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>106800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>121300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>106300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>109000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>96100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>96800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>102100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>97300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>114300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>143200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>135800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>140700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>116500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>121700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>99900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>109100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>93600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>101800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>98500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>97900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>87800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>90000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>92900</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1130,8 +1143,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1144,8 +1158,8 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
+      <c r="G12" s="3">
+        <v>17000</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
@@ -1231,8 +1245,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1332,83 +1349,86 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="H14" s="3">
-        <v>-2600</v>
+        <v>6300</v>
       </c>
       <c r="I14" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>36600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>4100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-1500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-1900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>120100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>12300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>700</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>20500</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
@@ -1425,39 +1445,42 @@
         <v>0</v>
       </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>7300</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>19800</v>
       </c>
-      <c r="AI14" s="3" t="s">
+      <c r="AJ14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>11200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>10900</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>11500</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>11700</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>11500</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>11300</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1534,8 +1557,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1568,210 +1594,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>308500</v>
+        <v>302700</v>
       </c>
       <c r="E17" s="3">
-        <v>265300</v>
+        <v>309500</v>
       </c>
       <c r="F17" s="3">
-        <v>290000</v>
+        <v>265900</v>
       </c>
       <c r="G17" s="3">
-        <v>280000</v>
+        <v>293900</v>
       </c>
       <c r="H17" s="3">
-        <v>300700</v>
+        <v>280400</v>
       </c>
       <c r="I17" s="3">
-        <v>286300</v>
+        <v>303600</v>
       </c>
       <c r="J17" s="3">
+        <v>286700</v>
+      </c>
+      <c r="K17" s="3">
         <v>350100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>299700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>312100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>260600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>305700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>287900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>265600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>236400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>256000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>262800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>242100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>381700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>311500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>304700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>314600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>281300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>333200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>302500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>249900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>217600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>235300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>226100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>218200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>205300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>233100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>222600</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>38100</v>
+        <v>41500</v>
       </c>
       <c r="E18" s="3">
-        <v>24400</v>
+        <v>37200</v>
       </c>
       <c r="F18" s="3">
-        <v>35100</v>
+        <v>23800</v>
       </c>
       <c r="G18" s="3">
+        <v>31200</v>
+      </c>
+      <c r="H18" s="3">
+        <v>30600</v>
+      </c>
+      <c r="I18" s="3">
+        <v>26000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>9100</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="L18" s="3">
+        <v>28100</v>
+      </c>
+      <c r="M18" s="3">
+        <v>34500</v>
+      </c>
+      <c r="N18" s="3">
+        <v>27400</v>
+      </c>
+      <c r="O18" s="3">
+        <v>33900</v>
+      </c>
+      <c r="P18" s="3">
+        <v>24800</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>29200</v>
+      </c>
+      <c r="R18" s="3">
+        <v>16900</v>
+      </c>
+      <c r="S18" s="3">
+        <v>20900</v>
+      </c>
+      <c r="T18" s="3">
+        <v>15800</v>
+      </c>
+      <c r="U18" s="3">
+        <v>17400</v>
+      </c>
+      <c r="V18" s="3">
+        <v>-93500</v>
+      </c>
+      <c r="W18" s="3">
+        <v>28000</v>
+      </c>
+      <c r="X18" s="3">
+        <v>43700</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>42900</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>16400</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>15800</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>33700</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>23000</v>
+      </c>
+      <c r="AE18" s="3">
         <v>31000</v>
       </c>
-      <c r="H18" s="3">
-        <v>28900</v>
-      </c>
-      <c r="I18" s="3">
-        <v>9500</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-14500</v>
-      </c>
-      <c r="K18" s="3">
-        <v>28100</v>
-      </c>
-      <c r="L18" s="3">
-        <v>34500</v>
-      </c>
-      <c r="M18" s="3">
-        <v>27400</v>
-      </c>
-      <c r="N18" s="3">
-        <v>33900</v>
-      </c>
-      <c r="O18" s="3">
-        <v>24800</v>
-      </c>
-      <c r="P18" s="3">
-        <v>29200</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>16900</v>
-      </c>
-      <c r="R18" s="3">
-        <v>20900</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="AF18" s="3">
+        <v>31300</v>
+      </c>
+      <c r="AG18" s="3">
+        <v>33500</v>
+      </c>
+      <c r="AH18" s="3">
         <v>15800</v>
       </c>
-      <c r="T18" s="3">
-        <v>17400</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-93500</v>
-      </c>
-      <c r="V18" s="3">
-        <v>28000</v>
-      </c>
-      <c r="W18" s="3">
-        <v>43700</v>
-      </c>
-      <c r="X18" s="3">
-        <v>42900</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>16400</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>3900</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>15800</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>33700</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>23000</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>31000</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>31300</v>
-      </c>
-      <c r="AF18" s="3">
-        <v>33500</v>
-      </c>
-      <c r="AG18" s="3">
-        <v>15800</v>
-      </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>6400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>25700</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1807,513 +1840,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-800</v>
+        <v>-300</v>
       </c>
       <c r="E20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="J20" s="3">
         <v>1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="K20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-6700</v>
-      </c>
-      <c r="H20" s="3">
-        <v>500</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-200</v>
       </c>
       <c r="N20" s="3">
         <v>-200</v>
       </c>
       <c r="O20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P20" s="3">
         <v>-900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1500</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-1100</v>
       </c>
       <c r="W20" s="3">
         <v>-1100</v>
       </c>
       <c r="X20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>48300</v>
+        <v>53000</v>
       </c>
       <c r="E21" s="3">
+        <v>48400</v>
+      </c>
+      <c r="F21" s="3">
         <v>36300</v>
       </c>
-      <c r="F21" s="3">
-        <v>45200</v>
-      </c>
       <c r="G21" s="3">
-        <v>36000</v>
+        <v>46800</v>
       </c>
       <c r="H21" s="3">
-        <v>40900</v>
+        <v>42400</v>
       </c>
       <c r="I21" s="3">
-        <v>19300</v>
+        <v>38700</v>
       </c>
       <c r="J21" s="3">
+        <v>19400</v>
+      </c>
+      <c r="K21" s="3">
         <v>-5600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>38900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>44600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>39300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>46300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>36700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>41800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>29500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>33500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>26100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>24400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-82700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>39500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>54900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>55300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>28600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>18300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>26500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>38900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>31200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>38300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>38000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>40300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>21400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>15900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>32500</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E22" s="3">
         <v>6200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>6800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>8200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>8300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>8500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>8100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>6900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>7400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>7700</v>
-      </c>
-      <c r="P22" s="3">
-        <v>7300</v>
       </c>
       <c r="Q22" s="3">
         <v>7300</v>
       </c>
       <c r="R22" s="3">
+        <v>7300</v>
+      </c>
+      <c r="S22" s="3">
         <v>13200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>5400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>5000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>5600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>5500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>6600</v>
-      </c>
-      <c r="X22" s="3">
-        <v>6800</v>
       </c>
       <c r="Y22" s="3">
         <v>6800</v>
       </c>
       <c r="Z22" s="3">
+        <v>6800</v>
+      </c>
+      <c r="AA22" s="3">
         <v>6200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>4900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>2000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>1600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>1400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E23" s="3">
         <v>31100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>19000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>26900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>16100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>21100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-24600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>20200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>25900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>20400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>26300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>16200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>21300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>8900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>6400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>7300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-100600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>21400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>36100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>35800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>8600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>9400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>28200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>20400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>28200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>28400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>31100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>12800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>6400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E24" s="3">
         <v>8600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>6100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-13200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>4900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>9900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>6300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-2600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>7600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>5300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>8700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>9000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>10200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>4200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>7400</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2413,210 +2462,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E26" s="3">
         <v>22600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>14200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>19600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>9900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>15800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-24600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>14100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>16800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>13300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>21800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>11000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>15500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>6900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>19600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-102200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>16400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>26200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>29500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>7100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>8200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>20600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>15100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>19500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>19400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>20900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>8500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>4700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E27" s="3">
         <v>22400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>14000</v>
       </c>
-      <c r="F27" s="3">
-        <v>19300</v>
-      </c>
       <c r="G27" s="3">
+        <v>19900</v>
+      </c>
+      <c r="H27" s="3">
         <v>9800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>15600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-24200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>13800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>16500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>13100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>21800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>11000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>15500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>6900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>19600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-102200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>16400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>26200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>29500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>7100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>8200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>20600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>15100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>19500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>19400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>20900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>8500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>4700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2716,8 +2774,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2766,8 +2827,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2787,11 +2848,11 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>6700</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2799,11 +2860,11 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-15200</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -2817,8 +2878,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2918,8 +2982,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3019,210 +3086,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="E32" s="3">
+        <v>200</v>
+      </c>
+      <c r="F32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G32" s="3">
+        <v>4100</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J32" s="3">
         <v>-1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="K32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="L32" s="3">
+        <v>200</v>
+      </c>
+      <c r="M32" s="3">
         <v>1400</v>
-      </c>
-      <c r="G32" s="3">
-        <v>6700</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="I32" s="3">
-        <v>1500</v>
-      </c>
-      <c r="J32" s="3">
-        <v>1900</v>
-      </c>
-      <c r="K32" s="3">
-        <v>200</v>
-      </c>
-      <c r="L32" s="3">
-        <v>1400</v>
-      </c>
-      <c r="M32" s="3">
-        <v>200</v>
       </c>
       <c r="N32" s="3">
         <v>200</v>
       </c>
       <c r="O32" s="3">
+        <v>200</v>
+      </c>
+      <c r="P32" s="3">
         <v>900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1500</v>
-      </c>
-      <c r="V32" s="3">
-        <v>1100</v>
       </c>
       <c r="W32" s="3">
         <v>1100</v>
       </c>
       <c r="X32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Y32" s="3">
         <v>300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>3200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>22400</v>
+        <v>28400</v>
       </c>
       <c r="E33" s="3">
-        <v>14000</v>
+        <v>22600</v>
       </c>
       <c r="F33" s="3">
-        <v>19300</v>
+        <v>14200</v>
       </c>
       <c r="G33" s="3">
-        <v>9800</v>
+        <v>19600</v>
       </c>
       <c r="H33" s="3">
-        <v>15600</v>
+        <v>9900</v>
       </c>
       <c r="I33" s="3">
+        <v>15800</v>
+      </c>
+      <c r="J33" s="3">
         <v>-700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-24200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>13800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>16500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>13100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>21800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>11000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>15500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>6900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>19600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-102200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>16400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>26200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>29500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>7100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>6400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>8200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>20600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>15100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>4300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>19400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>20900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>8500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>4700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3322,215 +3398,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>22400</v>
+        <v>28400</v>
       </c>
       <c r="E35" s="3">
-        <v>14000</v>
+        <v>22600</v>
       </c>
       <c r="F35" s="3">
-        <v>19300</v>
+        <v>14200</v>
       </c>
       <c r="G35" s="3">
-        <v>9800</v>
+        <v>19600</v>
       </c>
       <c r="H35" s="3">
-        <v>15600</v>
+        <v>9900</v>
       </c>
       <c r="I35" s="3">
+        <v>15800</v>
+      </c>
+      <c r="J35" s="3">
         <v>-700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-24200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>13800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>16500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>13100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>21800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>11000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>15500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>6900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>19600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-102200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>16400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>26200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>29500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>7100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>6400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>8200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>20600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>15100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>4300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>19400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>20900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>8500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>4700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45564</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45200</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45109</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45018</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44927</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44836</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44745</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44654</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44563</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44472</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44381</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44290</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44199</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44108</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44017</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43926</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43828</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43737</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43464</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43282</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43191</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43009</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42918</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42827</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42736</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3566,8 +3651,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3603,109 +3689,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>115600</v>
+      </c>
+      <c r="E41" s="3">
         <v>94200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>89800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>110500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>119600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>92900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>101300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>97600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>79400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>91700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>76100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>97300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>92800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>102400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>106900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>103100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>103700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>91800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>72700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>81300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>85200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>84300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>67000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>81000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>107300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>67000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>67900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>87000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>78100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>66800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>80000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>165700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>113700</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3805,435 +3895,450 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>173900</v>
+      </c>
+      <c r="E43" s="3">
         <v>179600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>147200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>163400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>143900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>166300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>147800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>182800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>170400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>174000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>145000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>171700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>153200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>146900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>128600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>139900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>132600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>139400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>145300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>177500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>176700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>183900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>165000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>179000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>177800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>156600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>137900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>142800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>133900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>136600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>116700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>126000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>128700</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>283100</v>
+      </c>
+      <c r="E44" s="3">
         <v>281100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>296200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>279100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>289300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>288200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>312700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>306300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>319100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>318100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>319400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>265100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>256700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>258200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>243100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>228700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>247500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>263700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>271200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>253600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>265100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>271800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>285700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>258700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>278800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>199100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>197400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>177900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>186100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>182800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>177700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>156100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>164200</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>37000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>32900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>30900</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3">
+        <v>3400</v>
+      </c>
+      <c r="K45" s="3">
+        <v>30300</v>
+      </c>
+      <c r="L45" s="3">
+        <v>34100</v>
+      </c>
+      <c r="M45" s="3">
+        <v>42900</v>
+      </c>
+      <c r="N45" s="3">
+        <v>43300</v>
+      </c>
+      <c r="O45" s="3">
+        <v>38300</v>
+      </c>
+      <c r="P45" s="3">
         <v>33000</v>
       </c>
-      <c r="H45" s="3">
-        <v>34100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>50000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>30300</v>
-      </c>
-      <c r="K45" s="3">
-        <v>34100</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="Q45" s="3">
+        <v>39100</v>
+      </c>
+      <c r="R45" s="3">
+        <v>38800</v>
+      </c>
+      <c r="S45" s="3">
+        <v>23700</v>
+      </c>
+      <c r="T45" s="3">
+        <v>31200</v>
+      </c>
+      <c r="U45" s="3">
+        <v>38400</v>
+      </c>
+      <c r="V45" s="3">
+        <v>44800</v>
+      </c>
+      <c r="W45" s="3">
+        <v>35800</v>
+      </c>
+      <c r="X45" s="3">
+        <v>37800</v>
+      </c>
+      <c r="Y45" s="3">
         <v>42900</v>
       </c>
-      <c r="M45" s="3">
-        <v>43300</v>
-      </c>
-      <c r="N45" s="3">
-        <v>38300</v>
-      </c>
-      <c r="O45" s="3">
-        <v>33000</v>
-      </c>
-      <c r="P45" s="3">
-        <v>39100</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>38800</v>
-      </c>
-      <c r="R45" s="3">
-        <v>23700</v>
-      </c>
-      <c r="S45" s="3">
-        <v>31200</v>
-      </c>
-      <c r="T45" s="3">
-        <v>38400</v>
-      </c>
-      <c r="U45" s="3">
-        <v>44800</v>
-      </c>
-      <c r="V45" s="3">
-        <v>35800</v>
-      </c>
-      <c r="W45" s="3">
-        <v>37800</v>
-      </c>
-      <c r="X45" s="3">
-        <v>42900</v>
-      </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>46800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>40200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>36300</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>38100</v>
       </c>
       <c r="AC45" s="3">
         <v>38100</v>
       </c>
       <c r="AD45" s="3">
+        <v>38100</v>
+      </c>
+      <c r="AE45" s="3">
         <v>23100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>24400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>24200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>26800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>33200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>608200</v>
+      </c>
+      <c r="E46" s="3">
         <v>591800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>566100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>583900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>585800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>581500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>611800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>617000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>603100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>626700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>583800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>572300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>535700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>546700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>517400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>495400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>515000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>533400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>533900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>548100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>564800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>582900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>564500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>558900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>600200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>460800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>441300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>430900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>422500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>410400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>401200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>470900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>438300</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4310,210 +4415,219 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>366600</v>
+      </c>
+      <c r="E48" s="3">
         <v>362400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>364100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>378700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>358000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>368700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>372100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>379600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>369500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>391300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>406100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>420400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>427700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>439600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>443200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>457000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>446400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>438300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>432400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>431600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>420000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>421800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>414000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>292900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>292600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>208000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>214700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>212600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>212300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>208700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>204400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>204500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>213600</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>159400</v>
+      </c>
+      <c r="E49" s="3">
         <v>154600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>157000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>161700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>156500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>162600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>162900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>162200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>174100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>193200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>212400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>223200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>230900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>240300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>239200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>253500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>240100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>226800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>219800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>346500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>343100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>353700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>334100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>343500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>353800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>67000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>70900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>68800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>68000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>66200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>63000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>61200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>65400</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4613,8 +4727,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4714,109 +4831,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>107300</v>
+        <v>87500</v>
       </c>
       <c r="E52" s="3">
-        <v>106400</v>
+        <v>84500</v>
       </c>
       <c r="F52" s="3">
-        <v>105900</v>
+        <v>83700</v>
       </c>
       <c r="G52" s="3">
-        <v>101300</v>
+        <v>82800</v>
       </c>
       <c r="H52" s="3">
-        <v>107200</v>
+        <v>83500</v>
       </c>
       <c r="I52" s="3">
-        <v>106500</v>
+        <v>88600</v>
       </c>
       <c r="J52" s="3">
+        <v>87400</v>
+      </c>
+      <c r="K52" s="3">
         <v>107700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>93900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>102200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>107500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>114200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>94900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>95600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>95500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>100000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>104200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>102500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>101000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>96800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>96700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>95900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>92500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>89300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>96300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>88800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>88600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>88300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>99600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>98700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>105000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>98800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4916,109 +5039,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1243300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1216100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1193500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1230100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1201600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1220000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1253200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1266500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1240600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1313400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1309800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1330100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1289200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1322200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1295300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1306000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1305800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1301000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1287100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1423000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1424500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1454300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1405100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1284600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1343000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>824600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>815500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>800600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>802400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>783900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>773700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>835400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>787500</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5054,8 +5183,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5091,186 +5221,190 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>78300</v>
+      </c>
+      <c r="E57" s="3">
         <v>78500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>74500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>62900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>75600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>69800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>85600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>78300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>83600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>92600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>87000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>85900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>72500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>82400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>72000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>58700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>63800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>64900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>68700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>75700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>72500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>67600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>73000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>66300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>69400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>61500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>55300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>50700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>52300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>49800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>48300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>45400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>48400</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>11100</v>
+        <v>24100</v>
       </c>
       <c r="E58" s="3">
-        <v>11000</v>
+        <v>23800</v>
       </c>
       <c r="F58" s="3">
-        <v>11200</v>
+        <v>23600</v>
       </c>
       <c r="G58" s="3">
-        <v>10700</v>
+        <v>23500</v>
       </c>
       <c r="H58" s="3">
-        <v>12400</v>
+        <v>21600</v>
       </c>
       <c r="I58" s="3">
-        <v>12400</v>
+        <v>24100</v>
       </c>
       <c r="J58" s="3">
+        <v>24000</v>
+      </c>
+      <c r="K58" s="3">
         <v>12300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>16400</v>
-      </c>
-      <c r="L58" s="3">
-        <v>16700</v>
       </c>
       <c r="M58" s="3">
         <v>16700</v>
       </c>
       <c r="N58" s="3">
+        <v>16700</v>
+      </c>
+      <c r="O58" s="3">
         <v>16800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>16900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>17100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>16900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>16800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>32700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>32500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>32300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>32500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>32900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>32200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>32100</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>31300</v>
       </c>
       <c r="AA58" s="3">
         <v>31300</v>
       </c>
       <c r="AB58" s="3">
-        <v>15000</v>
+        <v>31300</v>
       </c>
       <c r="AC58" s="3">
         <v>15000</v>
@@ -5293,412 +5427,427 @@
       <c r="AI58" s="3">
         <v>15000</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>15000</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>125100</v>
-      </c>
-      <c r="E59" s="3">
-        <v>122200</v>
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F59" s="3">
-        <v>140700</v>
+        <v>600</v>
       </c>
       <c r="G59" s="3">
-        <v>123800</v>
-      </c>
-      <c r="H59" s="3">
-        <v>112100</v>
-      </c>
-      <c r="I59" s="3">
-        <v>123500</v>
+        <v>22600</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J59" s="3">
+        <v>600</v>
+      </c>
+      <c r="K59" s="3">
         <v>129900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>137900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>140100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>142100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>159000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>145400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>130200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>128100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>117800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>148400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>135200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>129300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>155100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>149600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>134400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>127400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>126000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>137900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>103000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>99200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>111000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>101300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>92100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>92300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>98700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>90500</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>236400</v>
+      </c>
+      <c r="E60" s="3">
         <v>214700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>207700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>214700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>210200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>194300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>221500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>220500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>237900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>249400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>245900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>261800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>234800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>229600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>217100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>193300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>244800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>232600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>230300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>263300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>255000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>234300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>232500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>223600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>238500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>179500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>169600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>176600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>168700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>156900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>155600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>159100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>153900</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>384100</v>
+        <v>407500</v>
       </c>
       <c r="E61" s="3">
-        <v>388000</v>
+        <v>455600</v>
       </c>
       <c r="F61" s="3">
-        <v>413700</v>
+        <v>462200</v>
       </c>
       <c r="G61" s="3">
-        <v>440400</v>
+        <v>491900</v>
       </c>
       <c r="H61" s="3">
-        <v>469300</v>
+        <v>508000</v>
       </c>
       <c r="I61" s="3">
-        <v>495000</v>
+        <v>540400</v>
       </c>
       <c r="J61" s="3">
+        <v>566300</v>
+      </c>
+      <c r="K61" s="3">
         <v>514100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>510700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>534800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>509900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>506300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>513400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>545300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>550500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>563900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>551100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>590600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>597800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>566900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>595600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>642200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>611900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>587300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>617600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>228500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>228900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>214900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>219500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>215400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>208000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>255300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>202600</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>166100</v>
+        <v>64800</v>
       </c>
       <c r="E62" s="3">
-        <v>169300</v>
+        <v>63000</v>
       </c>
       <c r="F62" s="3">
-        <v>175800</v>
+        <v>62900</v>
       </c>
       <c r="G62" s="3">
-        <v>163500</v>
+        <v>37200</v>
       </c>
       <c r="H62" s="3">
-        <v>171500</v>
+        <v>58800</v>
       </c>
       <c r="I62" s="3">
-        <v>169700</v>
+        <v>64100</v>
       </c>
       <c r="J62" s="3">
+        <v>59200</v>
+      </c>
+      <c r="K62" s="3">
         <v>170400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>170700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>181900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>187200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>198600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>204200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>211700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>212900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>222200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>222800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>219600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>220300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>224700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>216600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>225700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>211000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>119100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>133900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>76000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>78600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>78900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>82000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>79700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>79000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>80300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>53600</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5798,8 +5947,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5899,8 +6051,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6000,109 +6155,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>741700</v>
+      </c>
+      <c r="E66" s="3">
         <v>765000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>764900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>804100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>814100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>835000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>886200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>905000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>919200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>966100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>942900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>966700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>952500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>986600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>980500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>979500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1018800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1042800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1048400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1054800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1067200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1102200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1055400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>930000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>990000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>484000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>477100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>470500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>470200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>452000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>442700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>494700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>410000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6138,8 +6299,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6239,8 +6401,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6340,8 +6505,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6441,8 +6609,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6542,109 +6713,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>384300</v>
+      </c>
+      <c r="E72" s="3">
         <v>356400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>334400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>320800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>301900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>292600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>277300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>278600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>303800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>290400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>274100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>261400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>240200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>229800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>214900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>208600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>189500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>184200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>180100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>286100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>273400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>251000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>225400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>222200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>219700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>215400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>198600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>187400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>183400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>168000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>150800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>140200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>139300</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6744,8 +6921,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6845,8 +7025,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6946,109 +7129,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>501600</v>
+      </c>
+      <c r="E76" s="3">
         <v>451200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>428500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>425900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>387600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>384900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>367000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>361500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>321400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>347400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>366900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>363400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>336800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>335600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>314800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>326500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>287000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>258200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>238700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>368200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>357400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>352100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>349700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>354700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>353000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>340600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>338400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>330100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>332200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>331900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>331000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>340700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>377500</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7148,215 +7337,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45564</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45200</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45109</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45018</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44927</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44836</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44745</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44654</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44563</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44472</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44381</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44290</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44199</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44108</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44017</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43926</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43828</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43737</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43464</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43282</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43191</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43009</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42918</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42827</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42736</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>22400</v>
+        <v>28400</v>
       </c>
       <c r="E81" s="3">
-        <v>14000</v>
+        <v>22600</v>
       </c>
       <c r="F81" s="3">
-        <v>19300</v>
+        <v>14200</v>
       </c>
       <c r="G81" s="3">
-        <v>9800</v>
+        <v>19600</v>
       </c>
       <c r="H81" s="3">
-        <v>15600</v>
+        <v>9900</v>
       </c>
       <c r="I81" s="3">
+        <v>15800</v>
+      </c>
+      <c r="J81" s="3">
         <v>-700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-24200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>13800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>16500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>13100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>21800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>11000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>15500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>6900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>19600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-102200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>16400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>26200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>29500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>7100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>6400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>8200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>20600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>15100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>4300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>19400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>20900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>8500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>4700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7392,109 +7590,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>10200</v>
+      </c>
+      <c r="F83" s="3">
+        <v>10000</v>
+      </c>
+      <c r="G83" s="3">
+        <v>9700</v>
+      </c>
+      <c r="H83" s="3">
+        <v>9800</v>
+      </c>
+      <c r="I83" s="3">
+        <v>10200</v>
+      </c>
+      <c r="J83" s="3">
+        <v>10700</v>
+      </c>
+      <c r="K83" s="3">
+        <v>10900</v>
+      </c>
+      <c r="L83" s="3">
         <v>11000</v>
       </c>
-      <c r="E83" s="3">
-        <v>10900</v>
-      </c>
-      <c r="F83" s="3">
-        <v>11500</v>
-      </c>
-      <c r="G83" s="3">
-        <v>11700</v>
-      </c>
-      <c r="H83" s="3">
-        <v>11500</v>
-      </c>
-      <c r="I83" s="3">
-        <v>11300</v>
-      </c>
-      <c r="J83" s="3">
-        <v>10900</v>
-      </c>
-      <c r="K83" s="3">
-        <v>11000</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>11400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>12000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>12600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>12800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>13200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>13400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>13900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>13100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>12700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>12200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>12700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>13300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>15000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>12300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>8500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>8700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>8100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>7800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>6200</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>8200</v>
       </c>
       <c r="AH83" s="3">
         <v>8200</v>
       </c>
       <c r="AI83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7594,8 +7796,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7695,8 +7900,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7796,8 +8004,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7897,8 +8108,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7998,109 +8212,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>76200</v>
+      </c>
+      <c r="E89" s="3">
         <v>21500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>12600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>27800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>66300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>18300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>29600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>28200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>27600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-17700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>22600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>28900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>10300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>24900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>21800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>64800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>48100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-15700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>51900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>69500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>32100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-11700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>33100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>53700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>10800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-5800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>35400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>46000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>14600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>7400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>19200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>44300</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8136,109 +8356,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-9600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-16100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-11200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-13500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-22200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-20800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-19000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-15000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-20000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-12500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-8900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-7400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-7700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-7500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-8100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-15700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-16300</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8338,8 +8562,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8439,109 +8666,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-9600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>1000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-10700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-14600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-11400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-13400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-22300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-20400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-18900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-14900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-20000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-26700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-413200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-8700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-8200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-7400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-7600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-6700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-8600</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8577,73 +8810,74 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1200</v>
+        <v>600</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="F96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-600</v>
+        <v>600</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-600</v>
+        <v>1200</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>-600</v>
       </c>
       <c r="L96" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
       <c r="N96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="O96" s="3">
         <v>-600</v>
       </c>
       <c r="P96" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
       <c r="R96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="S96" s="3">
         <v>-600</v>
       </c>
       <c r="T96" s="3">
+        <v>-600</v>
+      </c>
+      <c r="U96" s="3">
         <v>-4400</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
-        <v>-3800</v>
+        <v>0</v>
       </c>
       <c r="W96" s="3">
         <v>-3800</v>
       </c>
       <c r="X96" s="3">
-        <v>-3900</v>
+        <v>-3800</v>
       </c>
       <c r="Y96" s="3">
         <v>-3900</v>
@@ -8664,22 +8898,25 @@
         <v>-3900</v>
       </c>
       <c r="AE96" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-4000</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-3800</v>
       </c>
       <c r="AG96" s="3">
         <v>-3800</v>
       </c>
       <c r="AH96" s="3">
-        <v>-3900</v>
+        <v>-3800</v>
       </c>
       <c r="AI96" s="3">
         <v>-3900</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>-3900</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8779,8 +9016,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8880,8 +9120,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8981,307 +9224,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-52600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-7200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-29800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-30700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-31800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-28000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-21000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-9000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-32000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>18600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-7800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-31800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-13000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-12500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-45800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-16900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>32500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-36500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-47400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>17600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-31200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>400200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-5800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-19400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-28300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-22500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-86800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>42600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-11200</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-400</v>
+        <v>-1900</v>
       </c>
       <c r="E101" s="3">
+        <v>400</v>
+      </c>
+      <c r="F101" s="3">
+        <v>900</v>
+      </c>
+      <c r="G101" s="3">
+        <v>4100</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="J101" s="3">
         <v>-1600</v>
       </c>
-      <c r="F101" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="K101" s="3">
+        <v>4100</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="O101" s="3">
+        <v>300</v>
+      </c>
+      <c r="P101" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="Q101" s="3">
         <v>400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="R101" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="S101" s="3">
+        <v>4700</v>
+      </c>
+      <c r="T101" s="3">
+        <v>4200</v>
+      </c>
+      <c r="U101" s="3">
+        <v>1300</v>
+      </c>
+      <c r="V101" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="W101" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X101" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>700</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>800</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>900</v>
       </c>
-      <c r="J101" s="3">
-        <v>4100</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="N101" s="3">
-        <v>300</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="P101" s="3">
-        <v>400</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="R101" s="3">
-        <v>4700</v>
-      </c>
-      <c r="S101" s="3">
-        <v>4200</v>
-      </c>
-      <c r="T101" s="3">
-        <v>1300</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="V101" s="3">
-        <v>1200</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="X101" s="3">
-        <v>500</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>700</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>1800</v>
-      </c>
-      <c r="AF101" s="3">
-        <v>800</v>
-      </c>
-      <c r="AG101" s="3">
-        <v>2700</v>
-      </c>
-      <c r="AH101" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="AI101" s="3">
-        <v>900</v>
-      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E102" s="3">
         <v>4400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-20700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-9100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>26700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-8300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>18100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-12200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>15600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-21200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>4400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-9600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>11900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>19200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-8700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>17300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-26300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>40300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-19200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>8900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>11300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-13300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-85600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>51900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>25400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TILE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TILE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
   <si>
     <t>TILE</t>
   </si>
@@ -656,458 +656,470 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E7" s="2">
         <v>45564</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45200</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45109</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45018</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44927</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44836</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44745</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44654</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44563</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44472</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44381</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44290</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44199</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44108</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44017</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43926</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43828</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43737</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43464</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43282</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43191</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43009</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42918</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42827</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42736</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>335000</v>
+      </c>
+      <c r="E8" s="3">
         <v>344300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>346600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>289700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>325100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>311000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>329600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>295800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>335600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>327800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>346600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>288000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>339600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>312700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>294800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>253300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>276900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>278600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>259500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>288200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>339500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>348400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>357500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>297700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>337100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>318300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>283600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>240600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>266200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>257400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>251700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>221100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>239500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>248300</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>212700</v>
+      </c>
+      <c r="E9" s="3">
         <v>216600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>224000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>179300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>202000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>200700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>217800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>199900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>230100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>219000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>229900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>181200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>218300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>206400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>185800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>157200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>180100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>176500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>162200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>173900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>196300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>212600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>216800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>181200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>215400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>218400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>174500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>147000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>164400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>158900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>153800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>133300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>149500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>155400</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>122300</v>
+      </c>
+      <c r="E10" s="3">
         <v>127600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>122600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>110400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>123200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>110300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>111800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>95900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>105500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>108800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>116700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>106800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>121300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>106300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>109000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>96100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>96800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>102100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>97300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>114300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>143200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>135800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>140700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>116500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>121700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>99900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>109100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>93600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>101800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>98500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>97900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>87800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>90000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>92900</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1144,13 +1156,14 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>15100</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
@@ -1158,11 +1171,11 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3">
         <v>17000</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
@@ -1248,8 +1261,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1352,86 +1368,89 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>1500</v>
-      </c>
       <c r="H14" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I14" s="3">
         <v>6300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-2200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>36600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-1500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-1900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>120100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>12300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>700</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>20500</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
@@ -1448,43 +1467,46 @@
         <v>0</v>
       </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>7300</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>19800</v>
       </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E15" s="3">
         <v>11200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>11000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>10900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>11500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>11700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>11500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>11300</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1560,8 +1582,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1595,216 +1620,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>304400</v>
+      </c>
+      <c r="E17" s="3">
         <v>302700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>309500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>265900</v>
       </c>
-      <c r="G17" s="3">
-        <v>293900</v>
-      </c>
       <c r="H17" s="3">
+        <v>290200</v>
+      </c>
+      <c r="I17" s="3">
         <v>280400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>303600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>286700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>350100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>299700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>312100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>260600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>305700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>287900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>265600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>236400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>256000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>262800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>242100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>381700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>311500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>304700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>314600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>281300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>333200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>302500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>249900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>217600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>235300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>226100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>218200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>205300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>233100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>222600</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E18" s="3">
         <v>41500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>37200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>23800</v>
       </c>
-      <c r="G18" s="3">
-        <v>31200</v>
-      </c>
       <c r="H18" s="3">
+        <v>34900</v>
+      </c>
+      <c r="I18" s="3">
         <v>30600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>26000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-14500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>28100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>34500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>27400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>33900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>24800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>29200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>16900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>20900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>15800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>17400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-93500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>28000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>43700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>42900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>16400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>15800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>33700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>23000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>31000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>31300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>33500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>15800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>6400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>25700</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1841,528 +1873,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1600</v>
       </c>
-      <c r="G20" s="3">
-        <v>-4100</v>
-      </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>-1700</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-1200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-200</v>
       </c>
       <c r="O20" s="3">
         <v>-200</v>
       </c>
       <c r="P20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1500</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-1100</v>
       </c>
       <c r="X20" s="3">
         <v>-1100</v>
       </c>
       <c r="Y20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>45900</v>
+      </c>
+      <c r="E21" s="3">
         <v>53000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>48400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>36300</v>
       </c>
-      <c r="G21" s="3">
-        <v>46800</v>
-      </c>
       <c r="H21" s="3">
+        <v>48100</v>
+      </c>
+      <c r="I21" s="3">
         <v>42400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>38700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>19400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>38900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>44600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>39300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>46300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>36700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>41800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>29500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>33500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>26100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>24400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-82700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>39500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>54900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>55300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>28600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>18300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>26500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>38900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>31200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>38300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>38000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>40300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>21400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>15900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>32500</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E22" s="3">
         <v>5700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>6400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>6800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>8200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>8300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>8500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>8100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>7200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>7400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7700</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>7300</v>
       </c>
       <c r="R22" s="3">
         <v>7300</v>
       </c>
       <c r="S22" s="3">
+        <v>7300</v>
+      </c>
+      <c r="T22" s="3">
         <v>13200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>5400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>5000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>5600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>5500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>6600</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>6800</v>
       </c>
       <c r="Z22" s="3">
         <v>6800</v>
       </c>
       <c r="AA22" s="3">
+        <v>6800</v>
+      </c>
+      <c r="AB22" s="3">
         <v>6200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>4900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>2100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>2000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>1700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>1600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E23" s="3">
         <v>36100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>31100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>19000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>26900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>16100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>21100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-24600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>20200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>25900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>20400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>26300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>16200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>21300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>8900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>6400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>7500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>7300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-100600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>21400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>36100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>35800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>8600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>9400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>28200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>20400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>28200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>28400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>31100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>12800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>6400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E24" s="3">
         <v>7600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>6100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-13200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>9900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>6300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>7600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>5300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>8700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>9000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>10200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>4200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>7400</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2465,216 +2513,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E26" s="3">
         <v>28400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>22600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>14200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>19600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>9900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>15800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-24600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>14100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>16800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>13300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>21800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>11000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>15500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>6900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>19600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-102200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>16400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>26200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>29500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>7100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>8200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>20600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>15100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>19500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>19400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>20900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>8500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>28300</v>
+        <v>21800</v>
       </c>
       <c r="E27" s="3">
+        <v>28400</v>
+      </c>
+      <c r="F27" s="3">
         <v>22400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>14000</v>
       </c>
-      <c r="G27" s="3">
-        <v>19900</v>
-      </c>
       <c r="H27" s="3">
-        <v>9800</v>
+        <v>19600</v>
       </c>
       <c r="I27" s="3">
+        <v>9900</v>
+      </c>
+      <c r="J27" s="3">
         <v>15600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-24200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>13800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>16500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>13100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>21800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>11000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>15500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>6900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>19600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-102200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>16400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>26200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>29500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>7100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>8200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>20600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>15100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>19500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>19400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>20900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>8500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2777,8 +2834,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2830,8 +2890,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2851,11 +2911,11 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>6700</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2863,11 +2923,11 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-15200</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -2881,8 +2941,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2985,8 +3048,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3089,216 +3155,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1600</v>
       </c>
-      <c r="G32" s="3">
-        <v>4100</v>
-      </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>1200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1400</v>
-      </c>
-      <c r="N32" s="3">
-        <v>200</v>
       </c>
       <c r="O32" s="3">
         <v>200</v>
       </c>
       <c r="P32" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q32" s="3">
         <v>900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1500</v>
-      </c>
-      <c r="W32" s="3">
-        <v>1100</v>
       </c>
       <c r="X32" s="3">
         <v>1100</v>
       </c>
       <c r="Y32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Z32" s="3">
         <v>300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>3200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E33" s="3">
         <v>28400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>22600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>14200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>19600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>9900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>15800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-24200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>13800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>16500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>13100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>21800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>11000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>15500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>6900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>19600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-102200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>16400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>26200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>29500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>7100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>6400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>8200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>20600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>15100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>4300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>19400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>20900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>8500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3401,221 +3476,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E35" s="3">
         <v>28400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>22600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>14200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>19600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>9900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>15800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-24200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>13800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>16500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>13100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>21800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>11000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>15500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>6900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>19600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-102200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>16400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>26200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>29500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>7100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>6400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>8200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>20600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>15100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>4300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>19400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>20900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>8500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E38" s="2">
         <v>45564</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45200</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45109</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45018</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44927</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44836</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44745</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44654</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44563</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44472</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44381</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44290</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44199</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44108</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44017</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43926</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43828</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43737</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43464</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43282</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43191</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43009</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42918</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42827</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42736</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3652,8 +3736,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3690,112 +3775,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>99200</v>
+      </c>
+      <c r="E41" s="3">
         <v>115600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>94200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>89800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>110500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>119600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>92900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>101300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>97600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>79400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>91700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>76100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>97300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>92800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>102400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>106900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>103100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>103700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>91800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>72700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>81300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>85200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>84300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>67000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>81000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>107300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>67000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>67900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>87000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>78100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>66800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>80000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>165700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>113700</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3898,216 +3987,225 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>171100</v>
+      </c>
+      <c r="E43" s="3">
         <v>173900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>179600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>147200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>163400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>143900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>166300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>147800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>182800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>170400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>174000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>145000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>171700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>153200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>146900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>128600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>139900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>132600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>139400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>145300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>177500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>176700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>183900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>165000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>179000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>177800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>156600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>137900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>142800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>133900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>136600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>116700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>126000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>128700</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>260600</v>
+      </c>
+      <c r="E44" s="3">
         <v>283100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>281100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>296200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>279100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>289300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>288200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>312700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>306300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>319100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>318100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>319400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>265100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>256700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>258200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>243100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>228700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>247500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>263700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>271200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>253600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>265100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>271800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>285700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>258700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>278800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>199100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>197400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>177900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>186100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>182800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>177700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>156100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>164200</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4129,193 +4227,199 @@
       <c r="I45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>3400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>30300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>34100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>42900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>43300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>38300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>33000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>39100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>38800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>23700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>31200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>38400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>44800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>35800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>37800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>42900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>46800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>40200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>36300</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>38100</v>
       </c>
       <c r="AD45" s="3">
         <v>38100</v>
       </c>
       <c r="AE45" s="3">
+        <v>38100</v>
+      </c>
+      <c r="AF45" s="3">
         <v>23100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>24400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>24200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>26800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>33200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>564300</v>
+      </c>
+      <c r="E46" s="3">
         <v>608200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>591800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>566100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>583900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>585800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>581500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>611800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>617000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>603100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>626700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>583800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>572300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>535700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>546700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>517400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>495400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>515000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>533400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>533900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>548100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>564800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>582900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>564500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>558900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>600200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>460800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>441300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>430900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>422500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>410400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>401200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>470900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>438300</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4340,8 +4444,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4418,216 +4522,225 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>359200</v>
+      </c>
+      <c r="E48" s="3">
         <v>366600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>362400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>364100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>378700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>358000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>368700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>372100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>379600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>369500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>391300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>406100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>420400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>427700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>439600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>443200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>457000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>446400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>438300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>432400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>431600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>420000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>421800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>414000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>292900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>292600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>208000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>214700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>212600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>212300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>208700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>204400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>204500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>213600</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>148200</v>
+      </c>
+      <c r="E49" s="3">
         <v>159400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>154600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>157000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>161700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>156500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>162600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>162900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>162200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>174100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>193200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>212400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>223200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>230900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>240300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>239200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>253500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>240100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>226800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>219800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>346500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>343100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>353700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>334100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>343500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>353800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>67000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>70900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>68800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>68000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>66200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>63000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>61200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>65400</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4730,8 +4843,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4834,112 +4950,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>73400</v>
+      </c>
+      <c r="E52" s="3">
         <v>87500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>84500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>83700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>82800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>83500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>88600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>87400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>107700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>93900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>102200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>107500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>114200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>94900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>95600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>95500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>100000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>104200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>102500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>101000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>96800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>96700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>95900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>92500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>89300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>96300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>88800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>88600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>88300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>99600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>98700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>105000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>98800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5042,112 +5164,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1170800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1243300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1216100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1193500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1230100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1201600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1220000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1253200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1266500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1240600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1313400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1309800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1330100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1289200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1322200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1295300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1306000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1305800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1301000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1287100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1423000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1424500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1454300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1405100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1284600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1343000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>824600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>815500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>800600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>802400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>783900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>773700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>835400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>787500</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5184,8 +5312,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5222,192 +5351,196 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>68900</v>
+      </c>
+      <c r="E57" s="3">
         <v>78300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>78500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>74500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>62900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>75600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>69800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>85600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>78300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>83600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>92600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>87000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>85900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>72500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>82400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>72000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>58700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>63800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>64900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>68700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>75700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>72500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>67600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>73000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>66300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>69400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>61500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>55300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>50700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>52300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>49800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>48300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>45400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>48400</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E58" s="3">
         <v>24100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>23800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>23600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>23500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>21600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>24100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>24000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>16400</v>
-      </c>
-      <c r="M58" s="3">
-        <v>16700</v>
       </c>
       <c r="N58" s="3">
         <v>16700</v>
       </c>
       <c r="O58" s="3">
+        <v>16700</v>
+      </c>
+      <c r="P58" s="3">
         <v>16800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>16900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>17100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>16900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>16800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>32700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>32500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>32300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>32500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>32900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>32200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>32100</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>31300</v>
       </c>
       <c r="AB58" s="3">
         <v>31300</v>
       </c>
       <c r="AC58" s="3">
-        <v>15000</v>
+        <v>31300</v>
       </c>
       <c r="AD58" s="3">
         <v>15000</v>
@@ -5430,424 +5563,439 @@
       <c r="AJ58" s="3">
         <v>15000</v>
       </c>
+      <c r="AK58" s="3">
+        <v>15000</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>8</v>
+      <c r="D59" s="3">
+        <v>19000</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="3">
         <v>600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>22600</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K59" s="3">
         <v>600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>129900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>137900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>140100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>142100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>159000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>145400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>130200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>128100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>117800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>148400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>135200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>129300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>155100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>149600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>134400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>127400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>126000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>137900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>103000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>99200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>111000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>101300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>92100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>92300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>98700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>90500</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>216700</v>
+      </c>
+      <c r="E60" s="3">
         <v>236400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>214700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>207700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>214700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>210200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>194300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>221500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>220500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>237900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>249400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>245900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>261800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>234800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>229600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>217100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>193300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>244800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>232600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>230300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>263300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>255000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>234300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>232500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>223600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>238500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>179500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>169600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>176600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>168700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>156900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>155600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>159100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>153900</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>376200</v>
+      </c>
+      <c r="E61" s="3">
         <v>407500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>455600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>462200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>491900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>508000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>540400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>566300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>514100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>510700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>534800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>509900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>506300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>513400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>545300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>550500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>563900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>551100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>590600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>597800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>566900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>595600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>642200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>611900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>587300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>617600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>228500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>228900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>214900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>219500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>215400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>208000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>255300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>202600</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>32700</v>
+      </c>
+      <c r="E62" s="3">
         <v>64800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>63000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>62900</v>
       </c>
-      <c r="G62" s="3">
-        <v>37200</v>
-      </c>
       <c r="H62" s="3">
+        <v>42900</v>
+      </c>
+      <c r="I62" s="3">
         <v>58800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>64100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>59200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>170400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>170700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>181900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>187200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>198600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>204200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>211700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>212900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>222200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>222800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>219600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>220300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>224700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>216600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>225700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>211000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>119100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>133900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>76000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>78600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>78900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>82000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>79700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>79000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>80300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>53600</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5950,8 +6098,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6054,8 +6205,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6158,112 +6312,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>681700</v>
+      </c>
+      <c r="E66" s="3">
         <v>741700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>765000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>764900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>804100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>814100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>835000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>886200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>905000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>919200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>966100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>942900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>966700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>952500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>986600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>980500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>979500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1018800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1042800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1048400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1054800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1067200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1102200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1055400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>930000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>990000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>484000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>477100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>470500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>470200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>452000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>442700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>494700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>410000</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6300,8 +6460,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6404,8 +6565,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6508,8 +6672,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6612,8 +6779,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6716,112 +6886,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>405400</v>
+      </c>
+      <c r="E72" s="3">
         <v>384300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>356400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>334400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>320800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>301900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>292600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>277300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>278600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>303800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>290400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>274100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>261400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>240200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>229800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>214900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>208600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>189500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>184200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>180100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>286100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>273400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>251000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>225400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>222200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>219700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>215400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>198600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>187400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>183400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>168000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>150800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>140200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>139300</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6924,8 +7100,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7028,8 +7207,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7132,112 +7314,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>489100</v>
+      </c>
+      <c r="E76" s="3">
         <v>501600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>451200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>428500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>425900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>387600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>384900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>367000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>361500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>321400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>347400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>366900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>363400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>336800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>335600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>314800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>326500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>287000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>258200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>238700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>368200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>357400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>352100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>349700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>354700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>353000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>340600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>338400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>330100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>332200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>331900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>331000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>340700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>377500</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7340,221 +7528,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E80" s="2">
         <v>45564</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45200</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45109</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45018</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44927</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44836</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44745</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44654</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44563</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44472</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44381</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44290</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44199</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44108</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44017</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43926</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43828</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43737</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43464</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43282</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43191</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43009</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42918</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42827</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42736</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E81" s="3">
         <v>28400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>22600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>14200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>19600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>9900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>15800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-24200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>13800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>16500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>13100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>21800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>11000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>15500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>6900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>19600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-102200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>16400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>26200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>29500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>7100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>6400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>8200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>20600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>15100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>4300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>19400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>20900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>8500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7591,112 +7788,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E83" s="3">
         <v>10400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>10200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>10000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>9700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>9800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>10200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>10700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>10900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>11000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>11400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>12000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>12600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>12800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>13200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>13400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>13900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>13100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>12300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>12700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>12200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>12700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>13300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>15000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>12300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>8500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>8700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>8100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>7800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>6200</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>8200</v>
       </c>
       <c r="AI83" s="3">
         <v>8200</v>
       </c>
       <c r="AJ83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AK83" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7799,8 +8000,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7903,8 +8107,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8007,8 +8214,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8111,8 +8321,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8215,112 +8428,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E89" s="3">
         <v>76200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>21500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>12600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>27800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>66300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>18300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>29600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>28200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>27600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-17700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>22600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>28900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>10300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>24900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>21800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>64800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>48100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-15700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>51900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>69500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>32100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-11700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>33100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>53700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>10800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-5800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>35400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>46000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>14600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>7400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>19200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>44300</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8357,112 +8576,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-16100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-11200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-13500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-22200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-20800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-15000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-20000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-12500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-8900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-7400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-7700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-7500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-8100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-15700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-16300</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8565,8 +8788,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8669,112 +8895,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-9600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-8900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-10700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-14600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-11400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-13400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-22300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-20400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-18900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-14900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-20000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-26700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-413200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-8700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-8200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-7400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-7600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-6700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-8600</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8811,8 +9043,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8820,67 +9053,67 @@
         <v>600</v>
       </c>
       <c r="E96" s="3">
+        <v>600</v>
+      </c>
+      <c r="F96" s="3">
         <v>1200</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
         <v>600</v>
       </c>
       <c r="I96" s="3">
+        <v>600</v>
+      </c>
+      <c r="J96" s="3">
         <v>1200</v>
       </c>
-      <c r="J96" s="3" t="s">
+      <c r="K96" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-600</v>
       </c>
       <c r="L96" s="3">
         <v>-600</v>
       </c>
       <c r="M96" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
       <c r="O96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="P96" s="3">
         <v>-600</v>
       </c>
       <c r="Q96" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
       <c r="S96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="T96" s="3">
         <v>-600</v>
       </c>
       <c r="U96" s="3">
+        <v>-600</v>
+      </c>
+      <c r="V96" s="3">
         <v>-4400</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
-        <v>-3800</v>
+        <v>0</v>
       </c>
       <c r="X96" s="3">
         <v>-3800</v>
       </c>
       <c r="Y96" s="3">
-        <v>-3900</v>
+        <v>-3800</v>
       </c>
       <c r="Z96" s="3">
         <v>-3900</v>
@@ -8901,22 +9134,25 @@
         <v>-3900</v>
       </c>
       <c r="AF96" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-4000</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-3800</v>
       </c>
       <c r="AH96" s="3">
         <v>-3800</v>
       </c>
       <c r="AI96" s="3">
-        <v>-3900</v>
+        <v>-3800</v>
       </c>
       <c r="AJ96" s="3">
         <v>-3900</v>
       </c>
+      <c r="AK96" s="3">
+        <v>-3900</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9019,8 +9255,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9123,8 +9362,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9227,316 +9469,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-35700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-52600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-7200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-29800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-30700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-31800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-28000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-21000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-9000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-32000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>18600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-7800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-31800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-8300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-13000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-12500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-45800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-16900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>32500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-36500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-47400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>17600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-31200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>400200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-5800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-19400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-28300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-22500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-86800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>42600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-11200</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-3700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>4100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>4700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>4200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-3100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>2700</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-2900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="E102" s="3">
         <v>21400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-20700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-9100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>26700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-8300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>18100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-12200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>15600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-21200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-9600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>11900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>19200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-8700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>17300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-26300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>40300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-19200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>8900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>11300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-13300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-85600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>51900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>25400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TILE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TILE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
   <si>
     <t>TILE</t>
   </si>
@@ -656,470 +656,483 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45746</v>
+      </c>
+      <c r="E7" s="2">
         <v>45655</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45564</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45200</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45109</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45018</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44927</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44836</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44745</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44654</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44563</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44472</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44381</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44290</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44199</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44108</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44017</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43926</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43828</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43737</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43464</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43282</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43191</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43009</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42918</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42827</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42736</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>297400</v>
+      </c>
+      <c r="E8" s="3">
         <v>335000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>344300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>346600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>289700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>325100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>311000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>329600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>295800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>335600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>327800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>346600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>288000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>339600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>312700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>294800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>253300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>276900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>278600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>259500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>288200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>339500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>348400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>357500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>297700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>337100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>318300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>283600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>240600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>266200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>257400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>251700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>221100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>239500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>248300</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>186500</v>
+      </c>
+      <c r="E9" s="3">
         <v>212700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>216600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>224000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>179300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>202000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>200700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>217800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>199900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>230100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>219000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>229900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>181200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>218300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>206400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>185800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>157200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>180100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>176500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>162200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>173900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>196300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>212600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>216800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>181200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>215400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>218400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>174500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>147000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>164400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>158900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>153800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>133300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>149500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>155400</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E10" s="3">
         <v>122300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>127600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>122600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>110400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>123200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>110300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>111800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>95900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>105500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>108800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>116700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>106800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>121300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>106300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>109000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>96100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>96800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>102100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>97300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>114300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>143200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>135800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>140700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>116500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>121700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>99900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>109100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>93600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>101800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>98500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>97900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>87800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>90000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>92900</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1157,16 +1170,17 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
         <v>15100</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -1174,11 +1188,11 @@
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>17000</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -1264,8 +1278,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1371,89 +1388,92 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>2300</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>6300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-2200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>36600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>4100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-1500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-1900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>120100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>12300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>700</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>20500</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
@@ -1470,46 +1490,49 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>7300</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>19800</v>
       </c>
-      <c r="AK14" s="3" t="s">
+      <c r="AL14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E15" s="3">
         <v>11400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>11200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>11000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>10900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>11500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>11700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>11500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>11300</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1585,8 +1608,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1621,222 +1647,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>279700</v>
+      </c>
+      <c r="E17" s="3">
         <v>304400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>302700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>309500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>265900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>290200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>280400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>303600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>286700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>350100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>299700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>312100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>260600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>305700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>287900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>265600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>236400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>256000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>262800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>242100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>381700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>311500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>304700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>314600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>281300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>333200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>302500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>249900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>217600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>235300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>226100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>218200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>205300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>233100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>222600</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E18" s="3">
         <v>30600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>41500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>37200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>23800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>34900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>30600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>26000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-14500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>28100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>34500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>27400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>33900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>24800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>29200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>16900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>20900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>15800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>17400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-93500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>28000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>43700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>42900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>16400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>15800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>33700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>23000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>31000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>31300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>33500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>15800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>6400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>25700</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1874,543 +1907,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1700</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-200</v>
       </c>
       <c r="P20" s="3">
         <v>-200</v>
       </c>
       <c r="Q20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R20" s="3">
         <v>-900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-5100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1500</v>
-      </c>
-      <c r="X20" s="3">
-        <v>-1100</v>
       </c>
       <c r="Y20" s="3">
         <v>-1100</v>
       </c>
       <c r="Z20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>1400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E21" s="3">
         <v>45900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>53000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>48400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>36300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>48100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>42400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>38700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>19400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-5600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>38900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>44600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>39300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>46300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>36700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>41800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>29500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>33500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>26100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>24400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-82700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>39500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>54900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>55300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>28600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>18300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>26500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>38900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>31200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>38300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>38000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>40300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>21400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>15900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>32500</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E22" s="3">
         <v>4900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>5700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>6200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>6400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>6800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>8200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>8300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>8500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>8100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>7700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>7200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>7700</v>
-      </c>
-      <c r="R22" s="3">
-        <v>7300</v>
       </c>
       <c r="S22" s="3">
         <v>7300</v>
       </c>
       <c r="T22" s="3">
+        <v>7300</v>
+      </c>
+      <c r="U22" s="3">
         <v>13200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>5400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>5000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>5600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>5500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>6600</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>6800</v>
       </c>
       <c r="AA22" s="3">
         <v>6800</v>
       </c>
       <c r="AB22" s="3">
+        <v>6800</v>
+      </c>
+      <c r="AC22" s="3">
         <v>6200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>4900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>2300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>2100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>2000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>1900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>1700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>1400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E23" s="3">
         <v>27300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>36100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>31100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>19000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>26900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>16100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>21100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-24600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>20200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>25900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>20400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>26300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>16200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>21300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>8900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>7500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>7300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-100600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>21400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>36100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>35800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>8600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>9400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>28200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>20400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>28200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>28400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>31100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>12800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>6400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E24" s="3">
         <v>5600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>6100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>9100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-13200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>4900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>9900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>6300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>7600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>5300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>8700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>9000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>10200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>4200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>7400</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2516,222 +2565,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E26" s="3">
         <v>21800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>28400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>22600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>14200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>19600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>9900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>15800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-24600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>14100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>16800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>13300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>21800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>11000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>15500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>6900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>19600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>5900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-102200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>16400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>26200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>29500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>7100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>8200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>20600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>15100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>19500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>19400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>20900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>8500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>4700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E27" s="3">
         <v>21800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>28400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>22400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>14000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>19600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>9900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>15600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-24200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>13800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>16500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>13100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>21800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>11000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>15500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>6900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>19600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>5900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-102200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>16400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>26200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>29500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>7100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>8200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>20600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>15100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>19500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>19400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>20900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>8500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>4700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2837,8 +2895,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2893,8 +2954,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2914,11 +2975,11 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>6700</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2926,11 +2987,11 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-15200</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -2944,8 +3005,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3051,8 +3115,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3158,222 +3225,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E32" s="3">
         <v>3900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1700</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>1200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1400</v>
-      </c>
-      <c r="O32" s="3">
-        <v>200</v>
       </c>
       <c r="P32" s="3">
         <v>200</v>
       </c>
       <c r="Q32" s="3">
+        <v>200</v>
+      </c>
+      <c r="R32" s="3">
         <v>900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>5100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1500</v>
-      </c>
-      <c r="X32" s="3">
-        <v>1100</v>
       </c>
       <c r="Y32" s="3">
         <v>1100</v>
       </c>
       <c r="Z32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AA32" s="3">
         <v>300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>3200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E33" s="3">
         <v>21800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>28400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>22600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>14200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>19600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>9900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>15800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-24200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>13800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>16500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>13100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>21800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>11000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>15500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>6900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>19600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-102200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>16400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>26200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>29500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>7100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>6400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>8200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>20600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>15100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>4300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>19400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>20900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>8500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>4700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3479,227 +3555,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E35" s="3">
         <v>21800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>28400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>22600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>14200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>19600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>9900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>15800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-24200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>13800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>16500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>13100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>21800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>11000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>15500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>6900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>19600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-102200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>16400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>26200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>29500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>7100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>6400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>8200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>20600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>15100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>4300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>19400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>20900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>8500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>4700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45746</v>
+      </c>
+      <c r="E38" s="2">
         <v>45655</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45564</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45200</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45109</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45018</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44927</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44836</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44745</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44654</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44563</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44472</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44381</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44290</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44199</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44108</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44017</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43926</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43828</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43737</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43464</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43282</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43191</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43009</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42918</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42827</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42736</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3737,8 +3822,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3776,115 +3862,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>97800</v>
+      </c>
+      <c r="E41" s="3">
         <v>99200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>115600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>94200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>89800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>110500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>119600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>92900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>101300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>97600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>79400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>91700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>76100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>97300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>92800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>102400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>106900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>103100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>103700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>91800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>72700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>81300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>85200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>84300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>67000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>81000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>107300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>67000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>67900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>87000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>78100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>66800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>80000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>165700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>113700</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3990,222 +4080,231 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>162800</v>
+      </c>
+      <c r="E43" s="3">
         <v>171100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>173900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>179600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>147200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>163400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>143900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>166300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>147800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>182800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>170400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>174000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>145000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>171700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>153200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>146900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>128600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>139900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>132600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>139400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>145300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>177500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>176700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>183900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>165000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>179000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>177800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>156600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>137900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>142800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>133900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>136600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>116700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>126000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>128700</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>281700</v>
+      </c>
+      <c r="E44" s="3">
         <v>260600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>283100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>281100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>296200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>279100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>289300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>288200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>312700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>306300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>319100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>318100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>319400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>265100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>256700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>258200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>243100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>228700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>247500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>263700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>271200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>253600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>265100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>271800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>285700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>258700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>278800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>199100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>197400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>177900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>186100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>182800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>177700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>156100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>164200</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4230,196 +4329,202 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>3400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>30300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>34100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>42900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>43300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>38300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>33000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>39100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>38800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>23700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>31200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>38400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>44800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>35800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>37800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>42900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>46800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>40200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>36300</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>38100</v>
       </c>
       <c r="AE45" s="3">
         <v>38100</v>
       </c>
       <c r="AF45" s="3">
+        <v>38100</v>
+      </c>
+      <c r="AG45" s="3">
         <v>23100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>24400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>24200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>26800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>33200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>579400</v>
+      </c>
+      <c r="E46" s="3">
         <v>564300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>608200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>591800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>566100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>583900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>585800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>581500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>611800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>617000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>603100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>626700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>583800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>572300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>535700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>546700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>517400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>495400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>515000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>533400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>533900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>548100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>564800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>582900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>564500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>558900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>600200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>460800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>441300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>430900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>422500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>410400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>401200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>470900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>438300</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4447,8 +4552,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4525,222 +4630,231 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>361600</v>
+      </c>
+      <c r="E48" s="3">
         <v>359200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>366600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>362400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>364100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>378700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>358000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>368700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>372100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>379600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>369500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>391300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>406100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>420400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>427700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>439600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>443200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>457000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>446400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>438300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>432400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>431600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>420000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>421800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>414000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>292900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>292600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>208000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>214700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>212600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>212300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>208700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>204400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>204500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>213600</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>152300</v>
+      </c>
+      <c r="E49" s="3">
         <v>148200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>159400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>154600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>157000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>161700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>156500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>162600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>162900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>162200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>174100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>193200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>212400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>223200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>230900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>240300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>239200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>253500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>240100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>226800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>219800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>346500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>343100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>353700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>334100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>343500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>353800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>67000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>70900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>68800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>68000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>66200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>63000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>61200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>65400</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4846,8 +4960,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4953,8 +5070,11 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4962,106 +5082,109 @@
         <v>73400</v>
       </c>
       <c r="E52" s="3">
+        <v>73400</v>
+      </c>
+      <c r="F52" s="3">
         <v>87500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>84500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>83700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>82800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>83500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>88600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>87400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>107700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>93900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>102200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>107500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>114200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>94900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>95600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>95500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>100000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>104200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>102500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>101000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>96800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>96700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>95900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>92500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>89300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>96300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>88800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>88600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>88300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>99600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>98700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>105000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>98800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5167,115 +5290,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1191800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1170800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1243300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1216100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1193500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1230100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1201600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1220000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1253200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1266500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1240600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1313400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1309800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1330100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1289200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1322200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1295300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1306000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1305800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1301000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1287100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1423000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1424500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1454300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1405100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1284600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1343000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>824600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>815500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>800600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>802400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>783900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>773700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>835400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>787500</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5313,8 +5442,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5352,198 +5482,202 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>83000</v>
+      </c>
+      <c r="E57" s="3">
         <v>68900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>78300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>78500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>74500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>62900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>75600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>69800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>85600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>78300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>83600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>92600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>87000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>85900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>72500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>82400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>72000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>58700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>63800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>64900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>68700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>75700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>72500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>67600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>73000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>66300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>69400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>61500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>55300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>50700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>52300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>49800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>48300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>45400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>48400</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E58" s="3">
         <v>15400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>24100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>23800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>23600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>23500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>21600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>24100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>24000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>12300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>16400</v>
-      </c>
-      <c r="N58" s="3">
-        <v>16700</v>
       </c>
       <c r="O58" s="3">
         <v>16700</v>
       </c>
       <c r="P58" s="3">
+        <v>16700</v>
+      </c>
+      <c r="Q58" s="3">
         <v>16800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>16900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>17100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>16900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>16800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>32700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>32500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>32300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>32500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>32900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>32200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>32100</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>31300</v>
       </c>
       <c r="AC58" s="3">
         <v>31300</v>
       </c>
       <c r="AD58" s="3">
-        <v>15000</v>
+        <v>31300</v>
       </c>
       <c r="AE58" s="3">
         <v>15000</v>
@@ -5566,436 +5700,451 @@
       <c r="AK58" s="3">
         <v>15000</v>
       </c>
+      <c r="AL58" s="3">
+        <v>15000</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>600</v>
+      </c>
+      <c r="E59" s="3">
         <v>19000</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H59" s="3">
         <v>600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>22600</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L59" s="3">
         <v>600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>129900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>137900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>140100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>142100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>159000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>145400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>130200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>128100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>117800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>148400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>135200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>129300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>155100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>149600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>134400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>127400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>126000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>137900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>103000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>99200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>111000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>101300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>92100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>92300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>98700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>90500</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>210200</v>
+      </c>
+      <c r="E60" s="3">
         <v>216700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>236400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>214700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>207700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>214700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>210200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>194300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>221500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>220500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>237900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>249400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>245900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>261800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>234800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>229600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>217100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>193300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>244800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>232600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>230300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>263300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>255000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>234300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>232500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>223600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>238500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>179500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>169600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>176600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>168700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>156900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>155600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>159100</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>153900</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>377300</v>
+      </c>
+      <c r="E61" s="3">
         <v>376200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>407500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>455600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>462200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>491900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>508000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>540400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>566300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>514100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>510700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>534800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>509900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>506300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>513400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>545300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>550500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>563900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>551100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>590600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>597800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>566900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>595600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>642200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>611900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>587300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>617600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>228500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>228900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>214900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>219500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>215400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>208000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>255300</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>202600</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>58700</v>
+      </c>
+      <c r="E62" s="3">
         <v>32700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>64800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>63000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>62900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>42900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>58800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>64100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>59200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>170400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>170700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>181900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>187200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>198600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>204200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>211700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>212900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>222200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>222800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>219600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>220300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>224700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>216600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>225700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>211000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>119100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>133900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>76000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>78600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>78900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>82000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>79700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>79000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>80300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>53600</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6101,8 +6250,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6208,8 +6360,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6315,115 +6470,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>678700</v>
+      </c>
+      <c r="E66" s="3">
         <v>681700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>741700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>765000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>764900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>804100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>814100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>835000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>886200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>905000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>919200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>966100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>942900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>966700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>952500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>986600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>980500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>979500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1018800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1042800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1048400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1054800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1067200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1102200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1055400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>930000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>990000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>484000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>477100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>470500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>470200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>452000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>442700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>494700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>410000</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6461,8 +6622,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6568,8 +6730,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6675,8 +6840,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6782,8 +6950,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6889,115 +7060,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>417800</v>
+      </c>
+      <c r="E72" s="3">
         <v>405400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>384300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>356400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>334400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>320800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>301900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>292600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>277300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>278600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>303800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>290400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>274100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>261400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>240200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>229800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>214900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>208600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>189500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>184200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>180100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>286100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>273400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>251000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>225400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>222200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>219700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>215400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>198600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>187400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>183400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>168000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>150800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>140200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>139300</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7103,8 +7280,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7210,8 +7390,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7317,115 +7500,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>513100</v>
+      </c>
+      <c r="E76" s="3">
         <v>489100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>501600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>451200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>428500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>425900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>387600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>384900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>367000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>361500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>321400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>347400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>366900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>363400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>336800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>335600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>314800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>326500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>287000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>258200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>238700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>368200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>357400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>352100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>349700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>354700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>353000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>340600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>338400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>330100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>332200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>331900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>331000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>340700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>377500</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7531,227 +7720,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45746</v>
+      </c>
+      <c r="E80" s="2">
         <v>45655</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45564</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45200</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45109</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45018</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44927</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44836</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44745</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44654</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44563</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44472</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44381</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44290</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44199</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44108</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44017</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43926</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43828</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43737</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43464</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43282</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43191</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43009</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42918</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42827</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42736</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E81" s="3">
         <v>21800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>28400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>22600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>14200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>19600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>9900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>15800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-24200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>13800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>16500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>13100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>21800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>11000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>15500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>6900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>19600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-102200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>16400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>26200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>29500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>7100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>6400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>8200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>20600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>15100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>4300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>19400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>20900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>8500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>4700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7789,115 +7987,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E83" s="3">
         <v>10200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>10400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>10200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>10000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>9700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>9800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>10200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>10700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>10900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>11000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>11400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>12000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>12600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>12800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>13200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>13400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>13900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>13100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>12100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>12300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>12700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>12200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>12700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>13300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>15000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>12300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>8500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>8700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>8100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>7800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>6200</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>8200</v>
       </c>
       <c r="AJ83" s="3">
         <v>8200</v>
       </c>
       <c r="AK83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AL83" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8003,8 +8205,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8110,8 +8315,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8217,8 +8425,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8324,8 +8535,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8431,115 +8645,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E89" s="3">
         <v>38000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>76200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>21500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>12600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>27800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>66300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>18300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>29600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>28200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>27600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-17700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>22600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>28900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>10300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>24900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>21800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>64800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>48100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-15700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>51900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>69500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>32100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-11700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>33100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>53700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>10800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-5800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>35400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>46000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>14600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>7400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>19200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>44300</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8577,115 +8797,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-16100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-11200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-13500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-22200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-20800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-19000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-15000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-20000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-12500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-8900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-7400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-7700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-7500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-8100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-15700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-16300</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8791,8 +9015,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8898,115 +9125,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-9600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-14600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-11400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-13400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-22300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-20400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-18900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-14900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-20000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-26700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-413200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-8700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-8200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-7400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-7600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-6700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-8600</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9044,79 +9277,80 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="E96" s="3">
         <v>600</v>
       </c>
       <c r="F96" s="3">
+        <v>600</v>
+      </c>
+      <c r="G96" s="3">
         <v>1200</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
         <v>600</v>
       </c>
       <c r="J96" s="3">
+        <v>600</v>
+      </c>
+      <c r="K96" s="3">
         <v>1200</v>
       </c>
-      <c r="K96" s="3" t="s">
+      <c r="L96" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-600</v>
       </c>
       <c r="M96" s="3">
         <v>-600</v>
       </c>
       <c r="N96" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
       <c r="P96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="Q96" s="3">
         <v>-600</v>
       </c>
       <c r="R96" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
       <c r="T96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="U96" s="3">
         <v>-600</v>
       </c>
       <c r="V96" s="3">
+        <v>-600</v>
+      </c>
+      <c r="W96" s="3">
         <v>-4400</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
-        <v>-3800</v>
+        <v>0</v>
       </c>
       <c r="Y96" s="3">
         <v>-3800</v>
       </c>
       <c r="Z96" s="3">
-        <v>-3900</v>
+        <v>-3800</v>
       </c>
       <c r="AA96" s="3">
         <v>-3900</v>
@@ -9137,22 +9371,25 @@
         <v>-3900</v>
       </c>
       <c r="AG96" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-4000</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-3800</v>
       </c>
       <c r="AI96" s="3">
         <v>-3800</v>
       </c>
       <c r="AJ96" s="3">
-        <v>-3900</v>
+        <v>-3800</v>
       </c>
       <c r="AK96" s="3">
         <v>-3900</v>
       </c>
+      <c r="AL96" s="3">
+        <v>-3900</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9258,8 +9495,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9365,8 +9605,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9472,325 +9715,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-35700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-52600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-29800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-30700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-31800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-28000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-21000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-9000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-32000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>18600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-31800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-8300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-13000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-12500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-45800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-16900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>32500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-36500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-47400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>17600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-31200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>400200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-5800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-19400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-28300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-22500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-86800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>42600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-11200</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E101" s="3">
         <v>2600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>4100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-3600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>4100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-2800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>4700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>4200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-3100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>1800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>2700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-2900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-16400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>21400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-20700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>26700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-8300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>18100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-12200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>15600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-21200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-9600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>11900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>19200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-8700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>17300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-14000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-26300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>40300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-19200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>8900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>11300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-13300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-85600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>51900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>25400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TILE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TILE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
   <si>
     <t>TILE</t>
   </si>
@@ -656,483 +656,496 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="25" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45837</v>
+      </c>
+      <c r="E7" s="2">
         <v>45746</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45655</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45564</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45200</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45109</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45018</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44927</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44836</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44745</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44654</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44563</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44472</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44381</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44290</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44199</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44108</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44017</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43926</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43828</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43737</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43464</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43282</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43191</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43009</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42918</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42827</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42736</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>375500</v>
+      </c>
+      <c r="E8" s="3">
         <v>297400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>335000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>344300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>346600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>289700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>325100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>311000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>329600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>295800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>335600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>327800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>346600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>288000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>339600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>312700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>294800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>253300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>276900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>278600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>259500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>288200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>339500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>348400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>357500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>297700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>337100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>318300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>283600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>240600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>266200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>257400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>251700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>221100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>239500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>248300</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>227500</v>
+      </c>
+      <c r="E9" s="3">
         <v>186500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>212700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>216600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>224000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>179300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>202000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>200700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>217800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>199900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>230100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>219000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>229900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>181200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>218300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>206400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>185800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>157200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>180100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>176500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>162200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>173900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>196300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>212600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>216800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>181200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>215400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>218400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>174500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>147000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>164400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>158900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>153800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>133300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>149500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>155400</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>148000</v>
+      </c>
+      <c r="E10" s="3">
         <v>111000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>122300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>127600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>122600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>110400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>123200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>110300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>111800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>95900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>105500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>108800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>116700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>106800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>121300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>106300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>109000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>96100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>96800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>102100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>97300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>114300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>143200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>135800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>140700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>116500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>121700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>99900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>109100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>93600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>101800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>98500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>97900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>87800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>90000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>92900</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1171,19 +1184,20 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>15100</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1191,11 +1205,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>17000</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1281,8 +1295,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1391,92 +1408,95 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2300</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="3">
+        <v>200</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>6300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-2200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>36600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>4100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-1500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-1900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>120100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>12300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>700</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>20500</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
@@ -1493,49 +1513,52 @@
         <v>0</v>
       </c>
       <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
         <v>7300</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>19800</v>
       </c>
-      <c r="AL14" s="3" t="s">
+      <c r="AM14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E15" s="3">
         <v>10700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>11400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>11200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>11000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>10900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>11500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>11700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>11500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>11300</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1611,8 +1634,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1648,228 +1674,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>322200</v>
+      </c>
+      <c r="E17" s="3">
         <v>279700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>304400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>302700</v>
       </c>
-      <c r="G17" s="3">
-        <v>309500</v>
-      </c>
       <c r="H17" s="3">
+        <v>309300</v>
+      </c>
+      <c r="I17" s="3">
         <v>265900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>290200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>280400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>303600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>286700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>350100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>299700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>312100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>260600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>305700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>287900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>265600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>236400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>256000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>262800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>242100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>381700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>311500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>304700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>314600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>281300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>333200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>302500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>249900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>217600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>235300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>226100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>218200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>205300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>233100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>222600</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>53300</v>
+      </c>
+      <c r="E18" s="3">
         <v>17700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>30600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>41500</v>
       </c>
-      <c r="G18" s="3">
-        <v>37200</v>
-      </c>
       <c r="H18" s="3">
+        <v>37300</v>
+      </c>
+      <c r="I18" s="3">
         <v>23800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>34900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>30600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>26000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-14500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>28100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>34500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>27400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>33900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>24800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>29200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>16900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>20900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>15800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>17400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-93500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>28000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>43700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>42900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>16400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>15800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>33700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>23000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>31000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>31300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>33500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>15800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>6400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>25700</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1908,228 +1941,235 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1700</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-1200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-200</v>
       </c>
       <c r="Q20" s="3">
         <v>-200</v>
       </c>
       <c r="R20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S20" s="3">
         <v>-900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-5100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1500</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-1100</v>
       </c>
       <c r="Z20" s="3">
         <v>-1100</v>
       </c>
       <c r="AA20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>1400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>62300</v>
+      </c>
+      <c r="E21" s="3">
         <v>32200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>45900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>53000</v>
       </c>
-      <c r="G21" s="3">
-        <v>48400</v>
-      </c>
       <c r="H21" s="3">
+        <v>48500</v>
+      </c>
+      <c r="I21" s="3">
         <v>36300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>48100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>42400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>38700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>19400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-5600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>38900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>44600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>39300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>46300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>36700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>41800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>29500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>33500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>26100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>24400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-82700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>39500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>54900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>55300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>28600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>18300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>26500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>38900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>31200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>38300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>38000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>40300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>21400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>15900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>32500</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2137,329 +2177,338 @@
         <v>4400</v>
       </c>
       <c r="E22" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F22" s="3">
         <v>4900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>6200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>6400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>6800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>8200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>8300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>8500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>8100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>7700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>7200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>6900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>7400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>7700</v>
-      </c>
-      <c r="S22" s="3">
-        <v>7300</v>
       </c>
       <c r="T22" s="3">
         <v>7300</v>
       </c>
       <c r="U22" s="3">
+        <v>7300</v>
+      </c>
+      <c r="V22" s="3">
         <v>13200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>5400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>5000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>5600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>5500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>6600</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>6800</v>
       </c>
       <c r="AB22" s="3">
         <v>6800</v>
       </c>
       <c r="AC22" s="3">
+        <v>6800</v>
+      </c>
+      <c r="AD22" s="3">
         <v>6200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>4900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>2300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>2100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>2000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>1900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>1600</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>1400</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>44200</v>
+      </c>
+      <c r="E23" s="3">
         <v>17100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>27300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>36100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>31100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>19000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>26900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>16100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>21100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-24600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>20200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>25900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>20400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>26300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>16200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>21300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>8900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>7500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>7300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-100600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>21400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>36100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>35800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>8600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>9400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>28200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>20400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>28200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>28400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>31100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>12800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>6400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E24" s="3">
         <v>4100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>8600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>6100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-13200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>9900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>6300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>7600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>5300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>8700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>9000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>10200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>4200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>7400</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2568,228 +2617,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E26" s="3">
         <v>13000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>21800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>28400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>22600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>14200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>19600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>9900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>15800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-24600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>14100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>16800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>13300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>21800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>11000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>15500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>6900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>19600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-102200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>16400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>26200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>29500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>7100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>8200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>20600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>15100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>19500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>19400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>20900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>8500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>4700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E27" s="3">
         <v>13000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>21800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>28400</v>
       </c>
-      <c r="G27" s="3">
-        <v>22400</v>
-      </c>
       <c r="H27" s="3">
+        <v>22500</v>
+      </c>
+      <c r="I27" s="3">
         <v>14000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>19600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>9900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>15600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-24200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>13800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>16500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>13100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>21800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>11000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>15500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>6900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>19600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-102200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>16400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>26200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>29500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>7100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>8200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>20600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>15100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>19500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>19400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>20900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>8500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>4700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2898,8 +2956,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2957,8 +3018,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2978,11 +3039,11 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>6700</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2990,11 +3051,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-15200</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3008,8 +3069,11 @@
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3118,8 +3182,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3228,228 +3295,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E32" s="3">
         <v>3800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1700</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>1200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1400</v>
-      </c>
-      <c r="P32" s="3">
-        <v>200</v>
       </c>
       <c r="Q32" s="3">
         <v>200</v>
       </c>
       <c r="R32" s="3">
+        <v>200</v>
+      </c>
+      <c r="S32" s="3">
         <v>900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>5100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1500</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>1100</v>
       </c>
       <c r="Z32" s="3">
         <v>1100</v>
       </c>
       <c r="AA32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AB32" s="3">
         <v>300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>3200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>1400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E33" s="3">
         <v>13000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>21800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>28400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>22600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>14200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>19600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>9900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>15800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-24200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>13800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>16500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>13100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>21800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>11000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>15500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>6900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>19600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>4700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-102200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>16400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>26200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>29500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>7100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>6400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>8200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>20600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>15100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>4300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>19400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>20900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>8500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>4700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3558,233 +3634,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E35" s="3">
         <v>13000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>21800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>28400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>22600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>14200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>19600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>9900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>15800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-24200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>13800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>16500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>13100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>21800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>11000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>15500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>6900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>19600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>4700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-102200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>16400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>26200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>29500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>7100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>6400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>8200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>20600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>15100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>4300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>19400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>20900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>8500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>4700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45837</v>
+      </c>
+      <c r="E38" s="2">
         <v>45746</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45655</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45564</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45200</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45109</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45018</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44927</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44836</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44745</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44654</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44563</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44472</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44381</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44290</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44199</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44108</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44017</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43926</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43828</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43737</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43464</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43282</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43191</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43009</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42918</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42827</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42736</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3823,8 +3908,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3863,118 +3949,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>121700</v>
+      </c>
+      <c r="E41" s="3">
         <v>97800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>99200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>115600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>94200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>89800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>110500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>119600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>92900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>101300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>97600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>79400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>91700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>76100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>97300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>92800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>102400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>106900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>103100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>103700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>91800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>72700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>81300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>85200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>84300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>67000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>81000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>107300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>67000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>67900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>87000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>78100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>66800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>80000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>165700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>113700</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4083,228 +4173,237 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>194300</v>
+      </c>
+      <c r="E43" s="3">
         <v>162800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>171100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>173900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>179600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>147200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>163400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>143900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>166300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>147800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>182800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>170400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>174000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>145000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>171700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>153200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>146900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>128600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>139900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>132600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>139400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>145300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>177500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>176700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>183900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>165000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>179000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>177800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>156600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>137900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>142800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>133900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>136600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>116700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>126000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>128700</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>288200</v>
+      </c>
+      <c r="E44" s="3">
         <v>281700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>260600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>283100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>281100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>296200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>279100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>289300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>288200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>312700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>306300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>319100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>318100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>319400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>265100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>256700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>258200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>243100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>228700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>247500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>263700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>271200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>253600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>265100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>271800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>285700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>258700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>278800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>199100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>197400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>177900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>186100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>182800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>177700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>156100</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>164200</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4332,199 +4431,205 @@
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>3400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>30300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>34100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>42900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>43300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>38300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>33000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>39100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>38800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>23700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>31200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>38400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>44800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>35800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>37800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>42900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>46800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>40200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>36300</v>
-      </c>
-      <c r="AE45" s="3">
-        <v>38100</v>
       </c>
       <c r="AF45" s="3">
         <v>38100</v>
       </c>
       <c r="AG45" s="3">
+        <v>38100</v>
+      </c>
+      <c r="AH45" s="3">
         <v>23100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>24400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>24200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>26800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>33200</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>643100</v>
+      </c>
+      <c r="E46" s="3">
         <v>579400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>564300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>608200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>591800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>566100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>583900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>585800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>581500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>611800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>617000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>603100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>626700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>583800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>572300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>535700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>546700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>517400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>495400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>515000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>533400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>533900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>548100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>564800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>582900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>564500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>558900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>600200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>460800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>441300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>430900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>422500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>410400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>401200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>470900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>438300</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4555,8 +4660,8 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4633,228 +4738,237 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>372500</v>
+      </c>
+      <c r="E48" s="3">
         <v>361600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>359200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>366600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>362400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>364100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>378700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>358000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>368700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>372100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>379600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>369500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>391300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>406100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>420400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>427700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>439600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>443200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>457000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>446400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>438300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>432400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>431600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>420000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>421800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>414000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>292900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>292600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>208000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>214700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>212600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>212300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>208700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>204400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>204500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>213600</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>162800</v>
+      </c>
+      <c r="E49" s="3">
         <v>152300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>148200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>159400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>154600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>157000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>161700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>156500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>162600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>162900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>162200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>174100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>193200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>212400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>223200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>230900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>240300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>239200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>253500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>240100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>226800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>219800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>346500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>343100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>353700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>334100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>343500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>353800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>67000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>70900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>68800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>68000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>66200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>63000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>61200</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>65400</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4963,8 +5077,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5073,118 +5190,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>73400</v>
+        <v>73600</v>
       </c>
       <c r="E52" s="3">
         <v>73400</v>
       </c>
       <c r="F52" s="3">
+        <v>73400</v>
+      </c>
+      <c r="G52" s="3">
         <v>87500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>84500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>83700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>82800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>83500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>88600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>87400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>107700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>93900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>102200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>107500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>114200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>94900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>95600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>95500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>100000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>104200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>102500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>101000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>96800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>96700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>95900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>92500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>89300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>96300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>88800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>88600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>88300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>99600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>98700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>105000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>98800</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5293,118 +5416,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1278200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1191800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1170800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1243300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1216100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1193500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1230100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1201600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1220000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1253200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1266500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1240600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1313400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1309800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1330100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1289200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1322200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1295300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1306000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1305800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1301000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1287100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1423000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1424500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1454300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1405100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1284600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1343000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>824600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>815500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>800600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>802400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>783900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>773700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>835400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>787500</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5443,8 +5572,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5483,204 +5613,208 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>86600</v>
+      </c>
+      <c r="E57" s="3">
         <v>83000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>68900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>78300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>78500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>74500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>62900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>75600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>69800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>85600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>78300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>83600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>92600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>87000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>85900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>72500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>82400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>72000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>58700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>63800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>64900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>68700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>75700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>72500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>67600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>73000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>66300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>69400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>61500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>55300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>50700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>52300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>49800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>48300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>45400</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>48400</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E58" s="3">
         <v>15900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>15400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>24100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>23800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>23600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>23500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>21600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>24100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>24000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>12300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>16400</v>
-      </c>
-      <c r="O58" s="3">
-        <v>16700</v>
       </c>
       <c r="P58" s="3">
         <v>16700</v>
       </c>
       <c r="Q58" s="3">
+        <v>16700</v>
+      </c>
+      <c r="R58" s="3">
         <v>16800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>16900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>17100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>16900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>16800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>32700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>32500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>32300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>32500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>32900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>32200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>32100</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>31300</v>
       </c>
       <c r="AD58" s="3">
         <v>31300</v>
       </c>
       <c r="AE58" s="3">
-        <v>15000</v>
+        <v>31300</v>
       </c>
       <c r="AF58" s="3">
         <v>15000</v>
@@ -5703,448 +5837,463 @@
       <c r="AL58" s="3">
         <v>15000</v>
       </c>
+      <c r="AM58" s="3">
+        <v>15000</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3">
         <v>600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>19000</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3">
         <v>600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>22600</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M59" s="3">
         <v>600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>129900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>137900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>140100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>142100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>159000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>145400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>130200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>128100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>117800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>148400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>135200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>129300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>155100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>149600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>134400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>127400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>126000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>137900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>103000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>99200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>111000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>101300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>92100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>92300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>98700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>90500</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>223500</v>
+      </c>
+      <c r="E60" s="3">
         <v>210200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>216700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>236400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>214700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>207700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>214700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>210200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>194300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>221500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>220500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>237900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>249400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>245900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>261800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>234800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>229600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>217100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>193300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>244800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>232600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>230300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>263300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>255000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>234300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>232500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>223600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>238500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>179500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>169600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>176600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>168700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>156900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>155600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>159100</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>153900</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>381200</v>
+      </c>
+      <c r="E61" s="3">
         <v>377300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>376200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>407500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>455600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>462200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>491900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>508000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>540400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>566300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>514100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>510700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>534800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>509900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>506300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>513400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>545300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>550500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>563900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>551100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>590600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>597800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>566900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>595600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>642200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>611900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>587300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>617600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>228500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>228900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>214900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>219500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>215400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>208000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>255300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>202600</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>61900</v>
+      </c>
+      <c r="E62" s="3">
         <v>58700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>32700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>64800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>63000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>62900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>42900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>58800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>64100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>59200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>170400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>170700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>181900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>187200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>198600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>204200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>211700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>212900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>222200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>222800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>219600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>220300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>224700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>216600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>225700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>211000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>119100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>133900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>76000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>78600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>78900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>82000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>79700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>79000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>80300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>53600</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6253,8 +6402,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6363,8 +6515,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6473,118 +6628,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>703200</v>
+      </c>
+      <c r="E66" s="3">
         <v>678700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>681700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>741700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>765000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>764900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>804100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>814100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>835000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>886200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>905000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>919200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>966100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>942900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>966700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>952500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>986600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>980500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>979500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1018800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1042800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1048400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1054800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1067200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1102200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1055400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>930000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>990000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>484000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>477100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>470500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>470200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>452000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>442700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>494700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>410000</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6623,8 +6784,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6733,8 +6895,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6843,8 +7008,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6953,8 +7121,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7063,118 +7234,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>449800</v>
+      </c>
+      <c r="E72" s="3">
         <v>417800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>405400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>384300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>356400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>334400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>320800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>301900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>292600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>277300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>278600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>303800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>290400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>274100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>261400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>240200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>229800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>214900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>208600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>189500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>184200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>180100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>286100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>273400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>251000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>225400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>222200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>219700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>215400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>198600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>187400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>183400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>168000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>150800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>140200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>139300</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7283,8 +7460,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7393,8 +7573,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7503,118 +7686,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>575000</v>
+      </c>
+      <c r="E76" s="3">
         <v>513100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>489100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>501600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>451200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>428500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>425900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>387600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>384900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>367000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>361500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>321400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>347400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>366900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>363400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>336800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>335600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>314800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>326500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>287000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>258200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>238700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>368200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>357400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>352100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>349700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>354700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>353000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>340600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>338400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>330100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>332200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>331900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>331000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>340700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>377500</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7723,233 +7912,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45837</v>
+      </c>
+      <c r="E80" s="2">
         <v>45746</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45655</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45564</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45200</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45109</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45018</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44927</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44836</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44745</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44654</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44563</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44472</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44381</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44290</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44199</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44108</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44017</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43926</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43828</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43737</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43464</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43282</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43191</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43009</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42918</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42827</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42736</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E81" s="3">
         <v>13000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>21800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>28400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>22600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>14200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>19600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>9900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>15800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-24200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>13800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>16500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>13100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>21800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>11000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>15500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>6900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>19600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>4700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-102200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>16400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>26200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>29500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>7100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>6400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>8200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>20600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>15100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>4300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>19400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>20900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>8500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>4700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7988,118 +8186,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E83" s="3">
         <v>9600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>10200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>10400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>10200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>10000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>9700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>9800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>10200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>10700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>10900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>11000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>11400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>12000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>12600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>12800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>13200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>13400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>13900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>13100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>12100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>12300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>12700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>12200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>12700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>13300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>15000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>12300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>8500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>8700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>8100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>7800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>6200</v>
-      </c>
-      <c r="AJ83" s="3">
-        <v>8200</v>
       </c>
       <c r="AK83" s="3">
         <v>8200</v>
       </c>
       <c r="AL83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AM83" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8208,8 +8410,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8318,8 +8523,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8428,8 +8636,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8538,8 +8749,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8648,118 +8862,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E89" s="3">
         <v>11700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>38000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>76200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>21500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>12600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>27800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>66300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>18300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>29600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>28200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>27600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-17700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>22600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>28900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>10300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>24900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>21800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>64800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>48100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-15700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>51900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>69500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>32100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-11700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>33100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>53700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>10800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-5800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>35400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>46000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>14600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>7400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>19200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>44300</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8798,118 +9018,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-10700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-6900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-16100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-11200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-13500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-22200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-20800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-19000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-15000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-20000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-12500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-8900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-7400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-7700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-7500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-8100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-15700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-16300</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9018,8 +9242,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9128,118 +9355,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-9600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-6900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-14600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-11400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-13400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-22300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-20400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-18900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-14900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-20000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-26700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-413200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-8700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-8200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-7400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-7600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-6700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-8600</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9278,82 +9511,83 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E96" s="3">
         <v>100</v>
-      </c>
-      <c r="E96" s="3">
-        <v>600</v>
       </c>
       <c r="F96" s="3">
         <v>600</v>
       </c>
       <c r="G96" s="3">
+        <v>600</v>
+      </c>
+      <c r="H96" s="3">
         <v>1200</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
         <v>600</v>
       </c>
       <c r="K96" s="3">
+        <v>600</v>
+      </c>
+      <c r="L96" s="3">
         <v>1200</v>
       </c>
-      <c r="L96" s="3" t="s">
+      <c r="M96" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-600</v>
       </c>
       <c r="N96" s="3">
         <v>-600</v>
       </c>
       <c r="O96" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
       <c r="Q96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="R96" s="3">
         <v>-600</v>
       </c>
       <c r="S96" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
       <c r="U96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="V96" s="3">
         <v>-600</v>
       </c>
       <c r="W96" s="3">
+        <v>-600</v>
+      </c>
+      <c r="X96" s="3">
         <v>-4400</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
-        <v>-3800</v>
+        <v>0</v>
       </c>
       <c r="Z96" s="3">
         <v>-3800</v>
       </c>
       <c r="AA96" s="3">
-        <v>-3900</v>
+        <v>-3800</v>
       </c>
       <c r="AB96" s="3">
         <v>-3900</v>
@@ -9374,22 +9608,25 @@
         <v>-3900</v>
       </c>
       <c r="AH96" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-4000</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-3800</v>
       </c>
       <c r="AJ96" s="3">
         <v>-3800</v>
       </c>
       <c r="AK96" s="3">
-        <v>-3900</v>
+        <v>-3800</v>
       </c>
       <c r="AL96" s="3">
         <v>-3900</v>
       </c>
+      <c r="AM96" s="3">
+        <v>-3900</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9498,8 +9735,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9608,8 +9848,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9718,334 +9961,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-8700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-35700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-52600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-7200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-29800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-30700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-31800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-28000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-21000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-9000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-32000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>18600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-7800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-31800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-8300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-13000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-12500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-45800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-16900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>32500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-36500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-47400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>17600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-31200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>400200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-5800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-19400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-28300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-22500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-86800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>42600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-11200</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>4100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>4100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-2800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>4700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>4200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>1800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>800</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>2700</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-2900</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-16400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>21400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-20700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>26700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-8300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>18100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-12200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>15600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-21200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>4400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-9600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>11900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>19200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-8700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>17300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-14000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-26300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>40300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-19200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>8900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>11300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-13300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-85600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>51900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>25400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TILE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TILE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
   <si>
     <t>TILE</t>
   </si>
@@ -656,509 +656,521 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="26" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="27" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E7" s="2">
         <v>45928</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45837</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45746</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45655</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45564</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45200</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45109</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45018</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44927</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44836</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44745</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44654</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44563</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44472</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44381</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44290</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44199</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44108</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44017</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43926</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43828</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43737</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43464</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43282</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43191</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43009</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42918</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42827</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42736</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>349400</v>
+      </c>
+      <c r="E8" s="3">
         <v>364500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>375500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>297400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>335000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>344300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>346600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>289700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>325100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>311000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>329600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>295800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>335600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>327800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>346600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>288000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>339600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>312700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>294800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>253300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>276900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>278600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>259500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>288200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>339500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>348400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>357500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>297700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>337100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>318300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>283600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>240600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>266200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>257400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>251700</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>221100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>239500</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>248300</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>214600</v>
+      </c>
+      <c r="E9" s="3">
         <v>220900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>227500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>186500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>212700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>216600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>224000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>179300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>202000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>200700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>217800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>199900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>230100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>219000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>229900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>181200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>218300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>206400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>185800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>157200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>180100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>176500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>162200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>173900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>196300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>212600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>216800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>181200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>215400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>218400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>174500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>147000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>164400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>158900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>153800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>133300</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>149500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>155400</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>134800</v>
+      </c>
+      <c r="E10" s="3">
         <v>143600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>148000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>111000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>122300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>127600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>122600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>110400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>123200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>110300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>111800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>95900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>105500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>108800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>116700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>106800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>121300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>106300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>109000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>96100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>96800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>102100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>97300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>114300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>143200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>135800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>140700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>116500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>121700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>99900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>109100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>93600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>101800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>98500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>97900</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>87800</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>90000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>92900</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1199,13 +1211,14 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>16100</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
@@ -1213,11 +1226,11 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3">
         <v>15100</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
@@ -1225,11 +1238,11 @@
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="3">
         <v>17000</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -1315,8 +1328,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1431,98 +1447,101 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2500</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>2300</v>
-      </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>6300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-2200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>36600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>4100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-1500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>120100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>12300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>700</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>20500</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
         <v>0</v>
       </c>
@@ -1539,55 +1558,58 @@
         <v>0</v>
       </c>
       <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
         <v>7300</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>19800</v>
       </c>
-      <c r="AN14" s="3" t="s">
+      <c r="AO14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E15" s="3">
         <v>10400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>11200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>10700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>11400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>11200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>11000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>10900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>11500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>11700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>11500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>11300</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1663,8 +1685,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1702,240 +1727,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>317700</v>
+      </c>
+      <c r="E17" s="3">
         <v>311700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>322200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>279700</v>
       </c>
-      <c r="G17" s="3">
-        <v>304400</v>
-      </c>
       <c r="H17" s="3">
+        <v>304700</v>
+      </c>
+      <c r="I17" s="3">
         <v>302700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>309300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>265900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>290200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>280400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>303600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>286700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>350100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>299700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>312100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>260600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>305700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>287900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>265600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>236400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>256000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>262800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>242100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>381700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>311500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>304700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>314600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>281300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>333200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>302500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>249900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>217600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>235300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>226100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>218200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>205300</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>233100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>222600</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E18" s="3">
         <v>52800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>53300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>17700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>30300</v>
+      </c>
+      <c r="I18" s="3">
+        <v>41500</v>
+      </c>
+      <c r="J18" s="3">
+        <v>37300</v>
+      </c>
+      <c r="K18" s="3">
+        <v>23800</v>
+      </c>
+      <c r="L18" s="3">
+        <v>34900</v>
+      </c>
+      <c r="M18" s="3">
         <v>30600</v>
       </c>
-      <c r="H18" s="3">
-        <v>41500</v>
-      </c>
-      <c r="I18" s="3">
-        <v>37300</v>
-      </c>
-      <c r="J18" s="3">
-        <v>23800</v>
-      </c>
-      <c r="K18" s="3">
-        <v>34900</v>
-      </c>
-      <c r="L18" s="3">
-        <v>30600</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>26000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>9100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-14500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>28100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>34500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>27400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>33900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>24800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>29200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>16900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>20900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>15800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>17400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-93500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>28000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>43700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>42900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>16400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>15800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>33700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>23000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>31000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>31300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>33500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>15800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>6400</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>25700</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1976,588 +2008,604 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3800</v>
       </c>
-      <c r="G20" s="3">
-        <v>-3900</v>
-      </c>
       <c r="H20" s="3">
+        <v>700</v>
+      </c>
+      <c r="I20" s="3">
         <v>-300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1700</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-1200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-200</v>
       </c>
       <c r="S20" s="3">
         <v>-200</v>
       </c>
       <c r="T20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U20" s="3">
         <v>-900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1500</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>-1100</v>
       </c>
       <c r="AB20" s="3">
         <v>-1100</v>
       </c>
       <c r="AC20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-3200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>1400</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E21" s="3">
         <v>63400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>62300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>32200</v>
       </c>
-      <c r="G21" s="3">
-        <v>45900</v>
-      </c>
       <c r="H21" s="3">
+        <v>41000</v>
+      </c>
+      <c r="I21" s="3">
         <v>53000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>48500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>36300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>48100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>42400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>38700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>19400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-5600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>38900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>44600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>39300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>46300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>36700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>41800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>29500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>33500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>26100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>24400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-82700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>39500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>54900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>55300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>28600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>18300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>26500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>38900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>31200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>38300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>38000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>40300</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>21400</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>15900</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>32500</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E22" s="3">
         <v>4200</v>
-      </c>
-      <c r="E22" s="3">
-        <v>4400</v>
       </c>
       <c r="F22" s="3">
         <v>4400</v>
       </c>
       <c r="G22" s="3">
+        <v>4400</v>
+      </c>
+      <c r="H22" s="3">
         <v>4900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>5700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>6200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>6400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>6800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>8200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>8300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>8500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>8100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>7200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>6900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>7400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>7700</v>
-      </c>
-      <c r="U22" s="3">
-        <v>7300</v>
       </c>
       <c r="V22" s="3">
         <v>7300</v>
       </c>
       <c r="W22" s="3">
+        <v>7300</v>
+      </c>
+      <c r="X22" s="3">
         <v>13200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>5400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>5000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>5600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>5500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>6600</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>6800</v>
       </c>
       <c r="AD22" s="3">
         <v>6800</v>
       </c>
       <c r="AE22" s="3">
+        <v>6800</v>
+      </c>
+      <c r="AF22" s="3">
         <v>6200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>4900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>2300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>2100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>1900</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>1700</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>1600</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>1400</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E23" s="3">
         <v>48500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>44200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>17100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>27300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>36100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>31100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>19000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>26900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>16100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>21100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-24600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>20200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>25900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>20400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>26300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>16200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>21300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>8900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>7500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>7300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-100600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>21400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>36100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>35800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>8600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>9400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>28200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>20400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>28200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>28400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>31100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>12800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>6400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E24" s="3">
         <v>2300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>11600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>8600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>6100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>9100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-13200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>9900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>6300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>7600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>5300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>8700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>9000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>10200</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>4200</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>1700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>7400</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2672,240 +2720,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E26" s="3">
         <v>46100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>32600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>13000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>21800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>28400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>22600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>14200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>19600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>9900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>15800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-24600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>14100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>16800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>13300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>21800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>11000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>15500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>6900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>19600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-102200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>16400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>26200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>29500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>7100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>8200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>20600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>15100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>19500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>19400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>20900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>8500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>4700</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E27" s="3">
         <v>46100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>32600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>13000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>21800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>28400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>22500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>14000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>19600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>9900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>15600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-24200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>13800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>16500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>13100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>21800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>11000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>15500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>6900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>19600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-102200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>16400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>26200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>29500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>7100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>8200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>20600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>15100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>19500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>19400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>20900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>8500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>4700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3020,8 +3077,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3085,8 +3145,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -3106,11 +3166,11 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>6700</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -3118,11 +3178,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-15200</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
@@ -3136,8 +3196,11 @@
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3252,8 +3315,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3368,240 +3434,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3800</v>
       </c>
-      <c r="G32" s="3">
-        <v>3900</v>
-      </c>
       <c r="H32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I32" s="3">
         <v>300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1700</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>1200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1400</v>
-      </c>
-      <c r="R32" s="3">
-        <v>200</v>
       </c>
       <c r="S32" s="3">
         <v>200</v>
       </c>
       <c r="T32" s="3">
+        <v>200</v>
+      </c>
+      <c r="U32" s="3">
         <v>900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>5100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1500</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>1100</v>
       </c>
       <c r="AB32" s="3">
         <v>1100</v>
       </c>
       <c r="AC32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AD32" s="3">
         <v>300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>3200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>1000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>1400</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E33" s="3">
         <v>46100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>32600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>13000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>21800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>28400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>22600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>14200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>19600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>9900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>15800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-24200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>13800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>16500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>13100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>21800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>11000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>15500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>6900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>19600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-102200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>16400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>26200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>29500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>7100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>6400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>8200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>20600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>15100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>4300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>19400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>20900</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>8500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>4700</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3716,245 +3791,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E35" s="3">
         <v>46100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>32600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>13000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>21800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>28400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>22600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>14200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>19600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>9900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>15800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-24200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>13800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>16500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>13100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>21800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>11000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>15500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>6900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>19600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-102200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>16400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>26200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>29500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>7100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>6400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>8200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>20600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>15100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>4300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>19400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>20900</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>8500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>4700</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E38" s="2">
         <v>45928</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45837</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45746</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45655</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45564</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45200</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45109</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45018</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44927</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44836</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44745</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44654</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44563</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44472</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44381</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44290</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44199</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44108</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44017</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43926</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43828</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43737</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43464</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43282</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43191</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43009</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42918</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42827</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42736</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3995,8 +4079,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4037,124 +4122,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>71300</v>
+      </c>
+      <c r="E41" s="3">
         <v>187400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>121700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>97800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>99200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>115600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>94200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>89800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>110500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>119600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>92900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>101300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>97600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>79400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>91700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>76100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>97300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>92800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>102400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>106900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>103100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>103700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>91800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>72700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>81300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>85200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>84300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>67000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>81000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>107300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>67000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>67900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>87000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>78100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>66800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>80000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>165700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>113700</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4269,240 +4358,249 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>174500</v>
+      </c>
+      <c r="E43" s="3">
         <v>187100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>194300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>162800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>171100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>173900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>179600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>147200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>163400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>143900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>166300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>147800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>182800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>170400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>174000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>145000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>171700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>153200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>146900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>128600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>139900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>132600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>139400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>145300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>177500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>176700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>183900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>165000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>179000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>177800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>156600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>137900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>142800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>133900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>136600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>116700</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>126000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>128700</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>275000</v>
+      </c>
+      <c r="E44" s="3">
         <v>286800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>288200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>281700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>260600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>283100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>281100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>296200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>279100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>289300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>288200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>312700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>306300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>319100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>318100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>319400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>265100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>256700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>258200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>243100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>228700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>247500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>263700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>271200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>253600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>265100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>271800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>285700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>258700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>278800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>199100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>197400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>177900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>186100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>182800</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>177700</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>156100</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>164200</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4536,205 +4634,211 @@
       <c r="M45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O45" s="3">
         <v>3400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>30300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>34100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>42900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>43300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>38300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>33000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>39100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>38800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>23700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>31200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>38400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>44800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>35800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>37800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>42900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>46800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>40200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>36300</v>
-      </c>
-      <c r="AG45" s="3">
-        <v>38100</v>
       </c>
       <c r="AH45" s="3">
         <v>38100</v>
       </c>
       <c r="AI45" s="3">
+        <v>38100</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>23100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>24400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>24200</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>26800</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>33200</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>554800</v>
+      </c>
+      <c r="E46" s="3">
         <v>695100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>643100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>579400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>564300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>608200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>591800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>566100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>583900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>585800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>581500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>611800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>617000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>603100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>626700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>583800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>572300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>535700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>546700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>517400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>495400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>515000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>533400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>533900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>548100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>564800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>582900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>564500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>558900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>600200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>460800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>441300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>430900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>422500</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>410400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>401200</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>470900</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>438300</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4771,8 +4875,8 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4849,240 +4953,249 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>387600</v>
+      </c>
+      <c r="E48" s="3">
         <v>371700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>372500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>361600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>359200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>366600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>362400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>364100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>378700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>358000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>368700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>372100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>379600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>369500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>391300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>406100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>420400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>427700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>439600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>443200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>457000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>446400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>438300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>432400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>431600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>420000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>421800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>414000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>292900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>292600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>208000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>214700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>212600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>212300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>208700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>204400</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>204500</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>213600</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>163000</v>
+      </c>
+      <c r="E49" s="3">
         <v>162100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>162800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>152300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>148200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>159400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>154600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>157000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>161700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>156500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>162600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>162900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>162200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>174100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>193200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>212400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>223200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>230900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>240300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>239200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>253500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>240100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>226800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>219800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>346500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>343100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>353700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>334100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>343500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>353800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>67000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>70900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>68800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>68000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>66200</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>63000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>61200</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>65400</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5197,8 +5310,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5313,124 +5429,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>74700</v>
+      </c>
+      <c r="E52" s="3">
         <v>75500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>73600</v>
-      </c>
-      <c r="F52" s="3">
-        <v>73400</v>
       </c>
       <c r="G52" s="3">
         <v>73400</v>
       </c>
       <c r="H52" s="3">
+        <v>74500</v>
+      </c>
+      <c r="I52" s="3">
         <v>87500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>84500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>83700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>82800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>83500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>88600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>87400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>107700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>93900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>102200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>107500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>114200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>94900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>95600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>95500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>100000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>104200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>102500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>101000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>96800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>96700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>95900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>92500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>89300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>96300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>88800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>88600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>88300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>99600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>98700</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>105000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>98800</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5545,124 +5667,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1206500</v>
+      </c>
+      <c r="E54" s="3">
         <v>1330500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1278200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1191800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1170800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1243300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1216100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1193500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1230100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1201600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1220000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1253200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1266500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1240600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1313400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1309800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1330100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1289200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1322200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1295300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1306000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1305800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1301000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1287100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1423000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1424500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1454300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1405100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1284600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1343000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>824600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>815500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>800600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>802400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>783900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>773700</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>835400</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>787500</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5703,8 +5831,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5745,216 +5874,220 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>64800</v>
+      </c>
+      <c r="E57" s="3">
         <v>77800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>86600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>83000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>68900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>78300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>78500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>74500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>62900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>75600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>69800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>85600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>78300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>83600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>92600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>87000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>85900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>72500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>82400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>72000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>58700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>63800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>64900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>68700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>75700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>72500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>67600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>73000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>66300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>69400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>61500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>55300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>50700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>52300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>49800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>48300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>45400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>48400</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>16800</v>
+        <v>27700</v>
       </c>
       <c r="E58" s="3">
         <v>16800</v>
       </c>
       <c r="F58" s="3">
+        <v>16800</v>
+      </c>
+      <c r="G58" s="3">
         <v>15900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>15400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>24100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>23800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>23600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>23500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>21600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>24100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>24000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>12300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>16400</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>16700</v>
       </c>
       <c r="R58" s="3">
         <v>16700</v>
       </c>
       <c r="S58" s="3">
+        <v>16700</v>
+      </c>
+      <c r="T58" s="3">
         <v>16800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>16900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>17100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>16900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>16800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>32700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>32500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>32300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>32500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>32900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>32200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>32100</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>31300</v>
       </c>
       <c r="AF58" s="3">
         <v>31300</v>
       </c>
       <c r="AG58" s="3">
-        <v>15000</v>
+        <v>31300</v>
       </c>
       <c r="AH58" s="3">
         <v>15000</v>
@@ -5977,472 +6110,487 @@
       <c r="AN58" s="3">
         <v>15000</v>
       </c>
+      <c r="AO58" s="3">
+        <v>15000</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>8</v>
+      <c r="D59" s="3">
+        <v>19100</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="3">
         <v>600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>19000</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K59" s="3">
         <v>600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>22600</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O59" s="3">
         <v>600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>129900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>137900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>140100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>142100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>159000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>145400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>130200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>128100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>117800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>148400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>135200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>129300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>155100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>149600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>134400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>127400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>126000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>137900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>103000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>99200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>111000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>101300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>92100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>92300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>98700</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>90500</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>237100</v>
+      </c>
+      <c r="E60" s="3">
         <v>240200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>223500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>210200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>216700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>236400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>214700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>207700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>214700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>210200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>194300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>221500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>220500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>237900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>249400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>245900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>261800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>234800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>229600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>217100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>193300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>244800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>232600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>230300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>263300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>255000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>234300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>232500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>223600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>238500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>179500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>169600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>176600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>168700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>156900</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>155600</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>159100</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>153900</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>246800</v>
+      </c>
+      <c r="E61" s="3">
         <v>381500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>381200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>377300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>376200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>407500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>455600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>462200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>491900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>508000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>540400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>566300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>514100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>510700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>534800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>509900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>506300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>513400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>545300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>550500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>563900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>551100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>590600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>597800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>566900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>595600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>642200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>611900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>587300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>617600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>228500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>228900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>214900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>219500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>215400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>208000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>255300</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>202600</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>53900</v>
+      </c>
+      <c r="E62" s="3">
         <v>62000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>61900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>58700</v>
       </c>
-      <c r="G62" s="3">
-        <v>32700</v>
-      </c>
       <c r="H62" s="3">
+        <v>57000</v>
+      </c>
+      <c r="I62" s="3">
         <v>64800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>63000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>62900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>42900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>58800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>64100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>59200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>170400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>170700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>181900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>187200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>198600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>204200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>211700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>212900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>222200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>222800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>219600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>220300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>224700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>216600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>225700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>211000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>119100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>133900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>76000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>78600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>78900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>82000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>79700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>79000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>80300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>53600</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6557,8 +6705,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6673,8 +6824,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6789,124 +6943,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>565800</v>
+      </c>
+      <c r="E66" s="3">
         <v>709600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>703200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>678700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>681700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>741700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>765000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>764900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>804100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>814100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>835000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>886200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>905000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>919200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>966100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>942900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>966700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>952500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>986600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>980500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>979500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1018800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1042800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1048400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1054800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1067200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1102200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1055400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>930000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>990000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>484000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>477100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>470500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>470200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>452000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>442700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>494700</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>410000</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6947,8 +7107,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7063,8 +7224,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7179,8 +7343,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7295,8 +7462,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7411,124 +7581,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>518000</v>
+      </c>
+      <c r="E72" s="3">
         <v>494800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>449800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>417800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>405400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>384300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>356400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>334400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>320800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>301900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>292600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>277300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>278600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>303800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>290400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>274100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>261400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>240200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>229800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>214900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>208600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>189500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>184200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>180100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>286100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>273400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>251000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>225400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>222200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>219700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>215400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>198600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>187400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>183400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>168000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>150800</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>140200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>139300</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7643,8 +7819,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7759,8 +7938,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7875,124 +8057,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>640700</v>
+      </c>
+      <c r="E76" s="3">
         <v>621000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>575000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>513100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>489100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>501600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>451200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>428500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>425900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>387600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>384900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>367000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>361500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>321400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>347400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>366900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>363400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>336800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>335600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>314800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>326500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>287000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>258200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>238700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>368200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>357400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>352100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>349700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>354700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>353000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>340600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>338400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>330100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>332200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>331900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>331000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>340700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>377500</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8107,245 +8295,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E80" s="2">
         <v>45928</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45837</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45746</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45655</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45564</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45200</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45109</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45018</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44927</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44836</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44745</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44654</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44563</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44472</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44381</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44290</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44199</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44108</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44017</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43926</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43828</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43737</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43464</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43282</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43191</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43009</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42918</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42827</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42736</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E81" s="3">
         <v>46100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>32600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>13000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>21800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>28400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>22600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>14200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>19600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>9900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>15800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-24200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>13800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>16500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>13100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>21800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>11000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>15500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>6900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>19600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-102200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>16400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>26200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>29500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>7100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>6400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>8200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>20600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>15100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>4300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>19400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>20900</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>8500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>4700</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8386,124 +8583,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E83" s="3">
         <v>9900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>9700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>9600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>10200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>10400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>10200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>10000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>9700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>9800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>10200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>10700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>10900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>11000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>11400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>12000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>12600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>13200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>13400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>13900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>13100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>12100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>12300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>12700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>12200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>12700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>13300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>15000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>12300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>8500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>8700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>8100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>7800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>6200</v>
-      </c>
-      <c r="AL83" s="3">
-        <v>8200</v>
       </c>
       <c r="AM83" s="3">
         <v>8200</v>
       </c>
       <c r="AN83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AO83" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8618,8 +8819,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8734,8 +8938,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8850,8 +9057,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8966,8 +9176,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9082,124 +9295,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>49300</v>
+      </c>
+      <c r="E89" s="3">
         <v>76700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>30100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>11700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>38000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>76200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>21500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>12600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>27800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>66300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>18300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>29600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>28200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>27600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-17700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>22600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>28900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>10300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>24900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>21800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>64800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>48100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-15700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>51900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>69500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>32100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-11700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>33100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>53700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>10800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-5800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>35400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>46000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>14600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>7400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>19200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>44300</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9240,124 +9459,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-13700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-10700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-6900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-16100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-11200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-13500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-22200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-20800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-19000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-15000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-20000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-12500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-8900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-7400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-7700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-7500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-8100</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-15700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-16300</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9472,8 +9695,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9588,124 +9814,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-10700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-14600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-11400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-13400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-22300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-20400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-18900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-14900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-20000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-26700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-413200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-8700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-8200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-7400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-7600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-6700</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-8600</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9746,8 +9978,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9758,76 +9991,76 @@
         <v>1200</v>
       </c>
       <c r="F96" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G96" s="3">
         <v>100</v>
-      </c>
-      <c r="G96" s="3">
-        <v>600</v>
       </c>
       <c r="H96" s="3">
         <v>600</v>
       </c>
       <c r="I96" s="3">
+        <v>600</v>
+      </c>
+      <c r="J96" s="3">
         <v>1200</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="L96" s="3">
         <v>600</v>
       </c>
       <c r="M96" s="3">
+        <v>600</v>
+      </c>
+      <c r="N96" s="3">
         <v>1200</v>
       </c>
-      <c r="N96" s="3" t="s">
+      <c r="O96" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-600</v>
       </c>
       <c r="P96" s="3">
         <v>-600</v>
       </c>
       <c r="Q96" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
       <c r="S96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="T96" s="3">
         <v>-600</v>
       </c>
       <c r="U96" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
       <c r="W96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="X96" s="3">
         <v>-600</v>
       </c>
       <c r="Y96" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
-        <v>-3800</v>
+        <v>0</v>
       </c>
       <c r="AB96" s="3">
         <v>-3800</v>
       </c>
       <c r="AC96" s="3">
-        <v>-3900</v>
+        <v>-3800</v>
       </c>
       <c r="AD96" s="3">
         <v>-3900</v>
@@ -9848,22 +10081,25 @@
         <v>-3900</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-4000</v>
-      </c>
-      <c r="AK96" s="3">
-        <v>-3800</v>
       </c>
       <c r="AL96" s="3">
         <v>-3800</v>
       </c>
       <c r="AM96" s="3">
-        <v>-3900</v>
+        <v>-3800</v>
       </c>
       <c r="AN96" s="3">
         <v>-3900</v>
       </c>
+      <c r="AO96" s="3">
+        <v>-3900</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9978,8 +10214,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10094,8 +10333,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10210,352 +10452,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-145300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-35700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-52600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-29800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-30700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-31800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-28000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-21000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-9000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-32000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>18600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-7800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-31800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-8300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-13000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-12500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-45800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-16900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>32500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-36500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-47400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>17600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-31200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>400200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-5800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-19400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-28300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-22500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-86800</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>42600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-11200</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E101" s="3">
         <v>2900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>4100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>4100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-3700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>4700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>4200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>1800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>800</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>2700</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-2900</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-116000</v>
+      </c>
+      <c r="E102" s="3">
         <v>65700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>23900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-16400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>21400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>4400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-20700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-9100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>26700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-8300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>18100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>15600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-21200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>4400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-9600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>11900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>19200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-8700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>17300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-14000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-26300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>40300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-19200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>8900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>11300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-13300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-85600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>51900</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>25400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TILE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TILE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="92">
   <si>
     <t>TILE</t>
   </si>
@@ -656,521 +656,534 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="27" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46117</v>
+      </c>
+      <c r="E7" s="2">
         <v>46019</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45928</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45837</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45746</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45655</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45564</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45200</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45109</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45018</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44927</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44836</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44745</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44654</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44563</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44472</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44381</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44290</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44199</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44108</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44017</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43926</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43828</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43737</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43464</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43282</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43191</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43009</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42918</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42827</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42736</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>331000</v>
+      </c>
+      <c r="E8" s="3">
         <v>349400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>364500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>375500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>297400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>335000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>344300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>346600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>289700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>325100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>311000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>329600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>295800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>335600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>327800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>346600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>288000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>339600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>312700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>294800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>253300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>276900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>278600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>259500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>288200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>339500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>348400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>357500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>297700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>337100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>318300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>283600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>240600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>266200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>257400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>251700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>221100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>239500</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>248300</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>204300</v>
+      </c>
+      <c r="E9" s="3">
         <v>214600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>220900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>227500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>186500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>212700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>216600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>224000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>179300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>202000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>200700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>217800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>199900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>230100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>219000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>229900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>181200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>218300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>206400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>185800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>157200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>180100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>176500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>162200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>173900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>196300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>212600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>216800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>181200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>215400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>218400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>174500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>147000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>164400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>158900</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>153800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>133300</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>149500</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>155400</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>126700</v>
+      </c>
+      <c r="E10" s="3">
         <v>134800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>143600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>148000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>111000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>122300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>127600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>122600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>110400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>123200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>110300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>111800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>95900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>105500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>108800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>116700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>106800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>121300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>106300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>109000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>96100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>96800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>102100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>97300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>114300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>143200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>135800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>140700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>116500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>121700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>99900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>109100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>93600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>101800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>98500</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>97900</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>87800</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>90000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>92900</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1212,16 +1225,17 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
         <v>16100</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -1229,11 +1243,11 @@
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>15100</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -1241,11 +1255,11 @@
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3">
         <v>17000</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>8</v>
@@ -1331,8 +1345,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1450,101 +1467,104 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>-3800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2500</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-2600</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>6300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-2200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>36600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>4100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>120100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>12300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>700</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>20500</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
@@ -1561,58 +1581,61 @@
         <v>0</v>
       </c>
       <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
         <v>7300</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>19800</v>
       </c>
-      <c r="AO14" s="3" t="s">
+      <c r="AP14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E15" s="3">
         <v>9800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>10400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>11200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>10700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>11400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>11200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>11000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>10900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>11500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>11700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>11500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>11300</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1688,8 +1711,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1728,246 +1754,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>299700</v>
+      </c>
+      <c r="E17" s="3">
         <v>317700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>311700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>322200</v>
       </c>
-      <c r="G17" s="3">
-        <v>279700</v>
-      </c>
       <c r="H17" s="3">
+        <v>275000</v>
+      </c>
+      <c r="I17" s="3">
         <v>304700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>302700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>309300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>265900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>290200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>280400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>303600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>286700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>350100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>299700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>312100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>260600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>305700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>287900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>265600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>236400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>256000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>262800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>242100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>381700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>311500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>304700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>314600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>281300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>333200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>302500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>249900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>217600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>235300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>226100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>218200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>205300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>233100</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>222600</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>31400</v>
+      </c>
+      <c r="E18" s="3">
         <v>31700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>52800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>53300</v>
       </c>
-      <c r="G18" s="3">
-        <v>17700</v>
-      </c>
       <c r="H18" s="3">
+        <v>22400</v>
+      </c>
+      <c r="I18" s="3">
         <v>30300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>41500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>37300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>23800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>34900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>30600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>26000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>28100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>34500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>27400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>33900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>24800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>29200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>16900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>20900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>15800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>17400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-93500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>28000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>43700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>42900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>16400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>15800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>33700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>23000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>31000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>31300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>33500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>15800</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>6400</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>25700</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2009,603 +2042,619 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E20" s="3">
         <v>2000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2200</v>
       </c>
-      <c r="G20" s="3">
-        <v>-3800</v>
-      </c>
       <c r="H20" s="3">
+        <v>900</v>
+      </c>
+      <c r="I20" s="3">
         <v>700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1700</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-1200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-200</v>
       </c>
       <c r="T20" s="3">
         <v>-200</v>
       </c>
       <c r="U20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V20" s="3">
         <v>-900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1500</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>-1100</v>
       </c>
       <c r="AC20" s="3">
         <v>-1100</v>
       </c>
       <c r="AD20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-3200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-700</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>1400</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>41400</v>
+      </c>
+      <c r="E21" s="3">
         <v>39500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>63400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>62300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>32200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>41000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>53000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>48500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>36300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>48100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>42400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>38700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>19400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>38900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>44600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>39300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>46300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>36700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>41800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>29500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>33500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>26100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>24400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-82700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>39500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>54900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>55300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>28600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>18300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>26500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>38900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>31200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>38300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>38000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>40300</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>21400</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>15900</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>32500</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E22" s="3">
         <v>6500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4200</v>
-      </c>
-      <c r="F22" s="3">
-        <v>4400</v>
       </c>
       <c r="G22" s="3">
         <v>4400</v>
       </c>
       <c r="H22" s="3">
+        <v>4400</v>
+      </c>
+      <c r="I22" s="3">
         <v>4900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>6200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>6400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>6800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>8200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>8300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>8500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>8100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>7700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>7200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>6900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>7400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>7700</v>
-      </c>
-      <c r="V22" s="3">
-        <v>7300</v>
       </c>
       <c r="W22" s="3">
         <v>7300</v>
       </c>
       <c r="X22" s="3">
+        <v>7300</v>
+      </c>
+      <c r="Y22" s="3">
         <v>13200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>5400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>5000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>5600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>5500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>6600</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>6800</v>
       </c>
       <c r="AE22" s="3">
         <v>6800</v>
       </c>
       <c r="AF22" s="3">
+        <v>6800</v>
+      </c>
+      <c r="AG22" s="3">
         <v>6200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>4900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>2300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>2000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>1900</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>1700</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>1600</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>1400</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E23" s="3">
         <v>27100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>48500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>44200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>17100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>27300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>36100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>31100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>19000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>26900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>16100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>21100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-24600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>20200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>25900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>20400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>26300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>16200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>21300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>8900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>7500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>7300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-100600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>21400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>36100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>35800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>8600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>9400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>28200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>20400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>28200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>28400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>31100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>12800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>6400</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E24" s="3">
         <v>2700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>11600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>8600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>6100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>9100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-13200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>4900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>9900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>6300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>7600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>5300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>8700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>9000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>10200</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>4200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>1700</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>7400</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2723,246 +2772,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E26" s="3">
         <v>24400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>46100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>32600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>13000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>21800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>28400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>22600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>14200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>19600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>9900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>15800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-24600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>14100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>16800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>13300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>21800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>11000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>15500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>6900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>19600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>5900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-102200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>16400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>26200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>29500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>7100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>8200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>20600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>15100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>19500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>19400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>20900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>8500</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>4700</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E27" s="3">
         <v>24400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>46100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>32600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>13000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>21800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>28400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>22500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>14000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>9900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>15600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>13800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>16500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>13100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>21800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>11000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>15500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>6900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>19600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>5900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-102200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>16400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>26200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>29500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>7100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>8200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>20600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>15100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>19500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>19400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>20900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>8500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>4700</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3080,8 +3138,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3148,8 +3209,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -3169,11 +3230,11 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>6700</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -3181,11 +3242,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-15200</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
@@ -3199,8 +3260,11 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3318,8 +3382,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3437,246 +3504,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2200</v>
       </c>
-      <c r="G32" s="3">
-        <v>3800</v>
-      </c>
       <c r="H32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I32" s="3">
         <v>-700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1700</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>1200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1400</v>
-      </c>
-      <c r="S32" s="3">
-        <v>200</v>
       </c>
       <c r="T32" s="3">
         <v>200</v>
       </c>
       <c r="U32" s="3">
+        <v>200</v>
+      </c>
+      <c r="V32" s="3">
         <v>900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>5100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1500</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>1100</v>
       </c>
       <c r="AC32" s="3">
         <v>1100</v>
       </c>
       <c r="AD32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AE32" s="3">
         <v>300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>3200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>1000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>700</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>1400</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E33" s="3">
         <v>24400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>46100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>32600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>13000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>21800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>28400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>22600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>14200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>9900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>15800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>13800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>16500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>13100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>21800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>11000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>15500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>6900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>19600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>5900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>4700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-102200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>16400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>26200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>29500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>7100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>6400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>8200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>20600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>15100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>4300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>19400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>20900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>8500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>4700</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3794,251 +3870,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E35" s="3">
         <v>24400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>46100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>32600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>13000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>21800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>28400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>22600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>14200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>9900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>15800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>13800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>16500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>13100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>21800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>11000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>15500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>6900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>19600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>5900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>4700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-102200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>16400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>26200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>29500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>7100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>6400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>8200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>20600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>15100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>4300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>19400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>20900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>8500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>4700</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46117</v>
+      </c>
+      <c r="E38" s="2">
         <v>46019</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45928</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45837</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45746</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45655</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45564</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45200</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45109</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45018</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44927</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44836</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44745</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44654</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44563</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44472</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44381</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44290</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44199</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44108</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44017</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43926</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43828</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43737</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43464</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43282</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43191</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43009</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42918</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42827</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42736</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4080,8 +4165,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4123,127 +4209,131 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>61200</v>
+      </c>
+      <c r="E41" s="3">
         <v>71300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>187400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>121700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>97800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>99200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>115600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>94200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>89800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>110500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>119600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>92900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>101300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>97600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>79400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>91700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>76100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>97300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>92800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>102400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>106900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>103100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>103700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>91800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>72700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>81300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>85200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>84300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>67000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>81000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>107300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>67000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>67900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>87000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>78100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>66800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>80000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>165700</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>113700</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4361,246 +4451,255 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>163300</v>
+      </c>
+      <c r="E43" s="3">
         <v>174500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>187100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>194300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>162800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>171100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>173900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>179600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>147200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>163400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>143900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>166300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>147800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>182800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>170400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>174000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>145000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>171700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>153200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>146900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>128600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>139900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>132600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>139400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>145300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>177500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>176700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>183900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>165000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>179000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>177800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>156600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>137900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>142800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>133900</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>136600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>116700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>126000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>128700</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>294200</v>
+      </c>
+      <c r="E44" s="3">
         <v>275000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>286800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>288200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>281700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>260600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>283100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>281100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>296200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>279100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>289300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>288200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>312700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>306300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>319100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>318100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>319400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>265100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>256700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>258200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>243100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>228700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>247500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>263700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>271200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>253600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>265100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>271800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>285700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>258700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>278800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>199100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>197400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>177900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>186100</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>182800</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>177700</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>156100</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>164200</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4637,208 +4736,214 @@
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3">
         <v>3400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>30300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>34100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>42900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>43300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>38300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>33000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>39100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>38800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>23700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>31200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>38400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>44800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>35800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>37800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>42900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>46800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>40200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>36300</v>
-      </c>
-      <c r="AH45" s="3">
-        <v>38100</v>
       </c>
       <c r="AI45" s="3">
         <v>38100</v>
       </c>
       <c r="AJ45" s="3">
+        <v>38100</v>
+      </c>
+      <c r="AK45" s="3">
         <v>23100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>24400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>24200</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>26800</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>33200</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>562300</v>
+      </c>
+      <c r="E46" s="3">
         <v>554800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>695100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>643100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>579400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>564300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>608200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>591800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>566100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>583900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>585800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>581500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>611800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>617000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>603100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>626700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>583800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>572300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>535700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>546700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>517400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>495400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>515000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>533400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>533900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>548100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>564800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>582900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>564500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>558900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>600200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>460800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>441300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>430900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>422500</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>410400</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>401200</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>470900</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>438300</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4878,8 +4983,8 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4956,246 +5061,255 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>384600</v>
+      </c>
+      <c r="E48" s="3">
         <v>387600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>371700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>372500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>361600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>359200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>366600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>362400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>364100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>378700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>358000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>368700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>372100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>379600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>369500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>391300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>406100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>420400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>427700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>439600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>443200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>457000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>446400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>438300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>432400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>431600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>420000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>421800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>414000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>292900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>292600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>208000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>214700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>212600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>212300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>208700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>204400</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>204500</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>213600</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>159700</v>
+      </c>
+      <c r="E49" s="3">
         <v>163000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>162100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>162800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>152300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>148200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>159400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>154600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>157000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>161700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>156500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>162600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>162900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>162200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>174100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>193200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>212400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>223200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>230900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>240300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>239200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>253500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>240100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>226800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>219800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>346500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>343100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>353700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>334100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>343500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>353800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>67000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>70900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>68800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>68000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>66200</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>63000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>61200</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>65400</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5313,8 +5427,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5432,127 +5549,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>74300</v>
+      </c>
+      <c r="E52" s="3">
         <v>74700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>75500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>73600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>73400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>74500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>87500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>84500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>83700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>82800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>83500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>88600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>87400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>107700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>93900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>102200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>107500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>114200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>94900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>95600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>95500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>100000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>104200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>102500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>101000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>96800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>96700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>95900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>92500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>89300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>96300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>88800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>88600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>88300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>99600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>98700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>105000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>98800</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5670,127 +5793,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1205800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1206500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1330500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1278200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1191800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1170800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1243300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1216100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1193500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1230100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1201600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1220000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1253200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1266500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1240600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1313400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1309800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1330100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1289200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1322200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1295300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1306000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1305800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1301000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1287100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1423000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1424500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1454300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1405100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1284600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1343000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>824600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>815500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>800600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>802400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>783900</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>773700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>835400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>787500</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5832,8 +5961,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5875,222 +6005,226 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>88100</v>
+      </c>
+      <c r="E57" s="3">
         <v>64800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>77800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>86600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>83000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>68900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>78300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>78500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>74500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>62900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>75600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>69800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>85600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>78300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>83600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>92600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>87000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>85900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>72500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>82400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>72000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>58700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>63800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>64900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>68700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>75700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>72500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>67600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>73000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>66300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>69400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>61500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>55300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>50700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>52300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>49800</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>48300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>45400</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>48400</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E58" s="3">
         <v>27700</v>
-      </c>
-      <c r="E58" s="3">
-        <v>16800</v>
       </c>
       <c r="F58" s="3">
         <v>16800</v>
       </c>
       <c r="G58" s="3">
+        <v>16800</v>
+      </c>
+      <c r="H58" s="3">
         <v>15900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>15400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>24100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>23800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>23600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>23500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>21600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>24100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>24000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>12300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>16400</v>
-      </c>
-      <c r="R58" s="3">
-        <v>16700</v>
       </c>
       <c r="S58" s="3">
         <v>16700</v>
       </c>
       <c r="T58" s="3">
+        <v>16700</v>
+      </c>
+      <c r="U58" s="3">
         <v>16800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>16900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>17100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>16900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>16800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>32700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>32500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>32300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>32500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>32900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>32200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>32100</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>31300</v>
       </c>
       <c r="AG58" s="3">
         <v>31300</v>
       </c>
       <c r="AH58" s="3">
-        <v>15000</v>
+        <v>31300</v>
       </c>
       <c r="AI58" s="3">
         <v>15000</v>
@@ -6113,484 +6247,499 @@
       <c r="AO58" s="3">
         <v>15000</v>
       </c>
+      <c r="AP58" s="3">
+        <v>15000</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E59" s="3">
         <v>19100</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H59" s="3">
         <v>600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>19000</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L59" s="3">
         <v>600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>22600</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P59" s="3">
         <v>600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>129900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>137900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>140100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>142100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>159000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>145400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>130200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>128100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>117800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>148400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>135200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>129300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>155100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>149600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>134400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>127400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>126000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>137900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>103000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>99200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>111000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>101300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>92100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>92300</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>98700</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>90500</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>231300</v>
+      </c>
+      <c r="E60" s="3">
         <v>237100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>240200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>223500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>210200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>216700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>236400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>214700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>207700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>214700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>210200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>194300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>221500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>220500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>237900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>249400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>245900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>261800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>234800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>229600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>217100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>193300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>244800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>232600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>230300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>263300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>255000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>234300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>232500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>223600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>238500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>179500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>169600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>176600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>168700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>156900</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>155600</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>159100</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>153900</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>258500</v>
+      </c>
+      <c r="E61" s="3">
         <v>246800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>381500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>381200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>377300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>376200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>407500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>455600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>462200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>491900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>508000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>540400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>566300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>514100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>510700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>534800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>509900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>506300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>513400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>545300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>550500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>563900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>551100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>590600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>597800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>566900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>595600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>642200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>611900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>587300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>617600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>228500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>228900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>214900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>219500</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>215400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>208000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>255300</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>202600</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>58200</v>
+      </c>
+      <c r="E62" s="3">
         <v>53900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>62000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>61900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>58700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>57000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>64800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>63000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>62900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>42900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>58800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>64100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>59200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>170400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>170700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>181900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>187200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>198600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>204200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>211700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>212900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>222200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>222800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>219600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>220300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>224700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>216600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>225700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>211000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>119100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>133900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>76000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>78600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>78900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>82000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>79700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>79000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>80300</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>53600</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6708,8 +6857,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6827,8 +6979,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6946,127 +7101,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>571200</v>
+      </c>
+      <c r="E66" s="3">
         <v>565800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>709600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>703200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>678700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>681700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>741700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>765000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>764900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>804100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>814100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>835000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>886200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>905000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>919200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>966100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>942900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>966700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>952500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>986600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>980500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>979500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1018800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1042800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1048400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1054800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1067200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1102200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1055400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>930000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>990000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>484000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>477100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>470500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>470200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>452000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>442700</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>494700</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>410000</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7108,8 +7269,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7227,8 +7389,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7346,8 +7511,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7465,8 +7633,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7584,127 +7755,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>539700</v>
+      </c>
+      <c r="E72" s="3">
         <v>518000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>494800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>449800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>417800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>405400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>384300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>356400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>334400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>320800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>301900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>292600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>277300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>278600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>303800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>290400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>274100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>261400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>240200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>229800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>214900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>208600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>189500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>184200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>180100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>286100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>273400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>251000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>225400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>222200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>219700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>215400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>198600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>187400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>183400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>168000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>150800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>140200</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>139300</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7822,8 +7999,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7941,8 +8121,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8060,127 +8243,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>634600</v>
+      </c>
+      <c r="E76" s="3">
         <v>640700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>621000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>575000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>513100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>489100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>501600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>451200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>428500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>425900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>387600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>384900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>367000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>361500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>321400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>347400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>366900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>363400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>336800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>335600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>314800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>326500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>287000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>258200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>238700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>368200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>357400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>352100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>349700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>354700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>353000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>340600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>338400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>330100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>332200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>331900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>331000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>340700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>377500</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8298,251 +8487,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46117</v>
+      </c>
+      <c r="E80" s="2">
         <v>46019</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45928</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45837</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45746</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45655</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45564</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45200</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45109</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45018</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44927</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44836</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44745</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44654</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44563</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44472</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44381</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44290</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44199</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44108</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44017</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43926</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43828</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43737</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43464</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43282</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43191</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43009</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42918</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42827</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42736</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E81" s="3">
         <v>24400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>46100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>32600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>13000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>21800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>28400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>22600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>14200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>9900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>15800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>13800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>16500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>13100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>21800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>11000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>15500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>6900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>19600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>5900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>4700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-102200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>16400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>26200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>29500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>7100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>6400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>8200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>20600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>15100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>4300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>19400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>20900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>8500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>4700</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8584,127 +8782,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E83" s="3">
         <v>10100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>9900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>9700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>9600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>10200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>10400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>10200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>10000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>9700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>9800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>10200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>10700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>10900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>11000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>11400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>12000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>13200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>13400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>13900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>13100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>12100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>12300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>12700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>12200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>12700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>13300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>15000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>12300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>8500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>8700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>8100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>7800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>6200</v>
-      </c>
-      <c r="AM83" s="3">
-        <v>8200</v>
       </c>
       <c r="AN83" s="3">
         <v>8200</v>
       </c>
       <c r="AO83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AP83" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8822,8 +9024,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8941,8 +9146,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9060,8 +9268,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9179,8 +9390,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9298,127 +9512,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E89" s="3">
         <v>49300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>76700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>30100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>11700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>38000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>76200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>21500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>12600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>27800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>66300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>18300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>29600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>28200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>27600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-17700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>22600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>28900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>10300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>24900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>21800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>64800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>48100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-15700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>51900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>69500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>32100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-11700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>33100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>53700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>10800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-5800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>35400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>46000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>14600</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>7400</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>19200</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>44300</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9460,127 +9680,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-20700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-13700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-9600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-10700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-6900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-16100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-11200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-13500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-22200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-20800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-15000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-20000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-12500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-8900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-7400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-7700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-7500</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-8100</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-15700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-16300</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9698,8 +9922,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9817,127 +10044,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-20700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-10700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>1000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-10700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-6900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-14600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-11400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-13400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-22300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-20400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-18900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-14900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-20000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-26700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-413200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-8700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-8200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-7400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-7600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-6700</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-8600</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9979,13 +10212,14 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>1200</v>
+        <v>100</v>
       </c>
       <c r="E96" s="3">
         <v>1200</v>
@@ -9994,76 +10228,76 @@
         <v>1200</v>
       </c>
       <c r="G96" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H96" s="3">
         <v>100</v>
-      </c>
-      <c r="H96" s="3">
-        <v>600</v>
       </c>
       <c r="I96" s="3">
         <v>600</v>
       </c>
       <c r="J96" s="3">
+        <v>600</v>
+      </c>
+      <c r="K96" s="3">
         <v>1200</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="M96" s="3">
         <v>600</v>
       </c>
       <c r="N96" s="3">
+        <v>600</v>
+      </c>
+      <c r="O96" s="3">
         <v>1200</v>
       </c>
-      <c r="O96" s="3" t="s">
+      <c r="P96" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-600</v>
       </c>
       <c r="Q96" s="3">
         <v>-600</v>
       </c>
       <c r="R96" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
       <c r="T96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="U96" s="3">
         <v>-600</v>
       </c>
       <c r="V96" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
       <c r="X96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="Y96" s="3">
         <v>-600</v>
       </c>
       <c r="Z96" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
-        <v>-3800</v>
+        <v>0</v>
       </c>
       <c r="AC96" s="3">
         <v>-3800</v>
       </c>
       <c r="AD96" s="3">
-        <v>-3900</v>
+        <v>-3800</v>
       </c>
       <c r="AE96" s="3">
         <v>-3900</v>
@@ -10084,22 +10318,25 @@
         <v>-3900</v>
       </c>
       <c r="AK96" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-4000</v>
-      </c>
-      <c r="AL96" s="3">
-        <v>-3800</v>
       </c>
       <c r="AM96" s="3">
         <v>-3800</v>
       </c>
       <c r="AN96" s="3">
-        <v>-3900</v>
+        <v>-3800</v>
       </c>
       <c r="AO96" s="3">
         <v>-3900</v>
       </c>
+      <c r="AP96" s="3">
+        <v>-3900</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10217,8 +10454,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10336,8 +10576,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10455,361 +10698,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-145300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-8700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-35700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-52600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-29800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-30700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-31800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-28000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-21000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-32000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>18600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-7800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-31800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-8300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-13000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-12500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-45800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-16900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>32500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-36500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-47400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>17600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-31200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>400200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-5800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-19400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-28300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-22500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-86800</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>42600</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-11200</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-5000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>4100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-3600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>4700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>4200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>700</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>1800</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>800</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>2700</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-2900</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-116000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>65700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>23900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-16400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>21400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>4400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-20700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-9100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>26700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-8300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>18100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-12200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>15600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-21200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-9600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-4600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>11900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>19200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-8700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>17300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-14000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-26300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>40300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-19200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>8900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>11300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-13300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-85600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>51900</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>25400</v>
       </c>
     </row>
